--- a/演唱会列表.xlsx
+++ b/演唱会列表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
@@ -50,11 +50,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
   <si>
     <t>歌手</t>
   </si>
   <si>
+    <t>中文演唱会名称</t>
+  </si>
+  <si>
+    <t>英文演唱会名称</t>
+  </si>
+  <si>
     <t>地点省</t>
   </si>
   <si>
@@ -73,6 +79,12 @@
     <t>伍佰</t>
   </si>
   <si>
+    <t>摇滚巨星 2</t>
+  </si>
+  <si>
+    <t>ROCK STAR 2</t>
+  </si>
+  <si>
     <t>江西</t>
   </si>
   <si>
@@ -88,6 +100,12 @@
     <t>李荣浩</t>
   </si>
   <si>
+    <t>黑马</t>
+  </si>
+  <si>
+    <t>Dark Horse</t>
+  </si>
+  <si>
     <t>广东</t>
   </si>
   <si>
@@ -100,6 +118,12 @@
     <t>邓紫棋</t>
   </si>
   <si>
+    <t>我是邓紫棋</t>
+  </si>
+  <si>
+    <t>I AM GLORIA 2.0</t>
+  </si>
+  <si>
     <t>广西</t>
   </si>
   <si>
@@ -112,9 +136,21 @@
     <t>周传雄</t>
   </si>
   <si>
+    <t>念念不忘・再遇见</t>
+  </si>
+  <si>
+    <t>Unforgettable・Reunion</t>
+  </si>
+  <si>
     <t>孙燕姿</t>
   </si>
   <si>
+    <t>就在日落以后</t>
+  </si>
+  <si>
+    <t>AUT NIHILO</t>
+  </si>
+  <si>
     <t>深圳</t>
   </si>
   <si>
@@ -127,12 +163,24 @@
     <t>任贤齐</t>
   </si>
   <si>
+    <t>齐迹 2024</t>
+  </si>
+  <si>
+    <t>Miracle 2024</t>
+  </si>
+  <si>
     <t>佛山</t>
   </si>
   <si>
     <t>佛山国际体育文化演艺中心</t>
   </si>
   <si>
+    <t>摇滚巨星</t>
+  </si>
+  <si>
+    <t>ROCK STAR</t>
+  </si>
+  <si>
     <t>江苏</t>
   </si>
   <si>
@@ -145,6 +193,9 @@
     <t>陈奕迅</t>
   </si>
   <si>
+    <t>Another Eason’s LIFE</t>
+  </si>
+  <si>
     <t>北京</t>
   </si>
   <si>
@@ -152,6 +203,12 @@
   </si>
   <si>
     <t>五月天</t>
+  </si>
+  <si>
+    <t>就是演唱会 2016</t>
+  </si>
+  <si>
+    <t>Just Rock It 2016</t>
   </si>
   <si>
     <t>陕西</t>
@@ -194,7 +251,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,18 +269,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF1F2328"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1F2328"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF1F2328"/>
       <name val="宋体"/>
@@ -709,137 +754,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -862,12 +907,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1181,19 +1220,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.4444444444444" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.6666666666667" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.1111111111111" style="2" customWidth="1"/>
-    <col min="4" max="4" width="28.8888888888889" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9" style="5" customWidth="1"/>
-    <col min="6" max="6" width="9" style="5"/>
-    <col min="7" max="7" width="15.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="25.2222222222222" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.7777777777778" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.6666666666667" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14.1111111111111" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.8888888888889" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9" style="5" customWidth="1"/>
+    <col min="8" max="8" width="9" style="5"/>
+    <col min="9" max="9" width="15.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:6">
+    <row r="1" ht="15.6" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1206,192 +1247,294 @@
       <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="15.6" spans="1:6">
-      <c r="A2" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H4" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H5" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2024</v>
+      </c>
+      <c r="H7" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5">
-        <v>2026</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="B8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2023</v>
+      </c>
+      <c r="H8" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="15.6" spans="1:6">
-      <c r="A3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="5">
-        <v>2026</v>
-      </c>
-      <c r="F3" s="5" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2016</v>
+      </c>
+      <c r="H9" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="15.6" spans="1:6">
-      <c r="A4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="5">
-        <v>2025</v>
-      </c>
-      <c r="F4" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="15.6" spans="1:6">
-      <c r="A5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="5">
-        <v>2025</v>
-      </c>
-      <c r="F5" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" ht="15.6" spans="1:6">
-      <c r="A6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="5">
-        <v>2025</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" ht="15.6" spans="1:6">
-      <c r="A7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="5">
-        <v>2024</v>
-      </c>
-      <c r="F7" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="19.2" spans="1:6">
-      <c r="A8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="5">
-        <v>2023</v>
-      </c>
-      <c r="F8" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" ht="15.6" spans="1:6">
-      <c r="A9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="5">
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="5">
         <v>2016</v>
       </c>
-      <c r="F9" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" ht="15.6" spans="1:6">
-      <c r="A10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="5">
-        <v>2016</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>37</v>
-      </c>
+      <c r="H10" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1412,24 +1555,24 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" cm="1">
-        <f t="array" ref="B2">COUNTA(_xlfn.UNIQUE(列表!C2:C11))</f>
+        <f t="array" ref="B2">COUNTA(_xlfn.UNIQUE(列表!E2:E11))</f>
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2" cm="1">
         <f t="array" ref="B3">COUNTA(_xlfn.UNIQUE(列表!A2:A10))</f>
@@ -1438,19 +1581,19 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B4" s="2">
-        <f>COUNT(列表!E:E)</f>
+        <f>COUNT(列表!G:G)</f>
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" cm="1">
-        <f t="array" ref="B5">COUNTA(_xlfn.UNIQUE(列表!E2:E12))</f>
+        <f t="array" ref="B5">COUNTA(_xlfn.UNIQUE(列表!G2:G12))</f>
         <v>5</v>
       </c>
     </row>

--- a/演唱会列表.xlsx
+++ b/演唱会列表.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
   <si>
     <t>歌手</t>
   </si>
@@ -79,9 +79,6 @@
     <t>伍佰</t>
   </si>
   <si>
-    <t>摇滚巨星 2</t>
-  </si>
-  <si>
     <t>ROCK STAR 2</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>邓紫棋</t>
   </si>
   <si>
-    <t>我是邓紫棋</t>
-  </si>
-  <si>
     <t>I AM GLORIA 2.0</t>
   </si>
   <si>
@@ -175,9 +169,6 @@
     <t>佛山国际体育文化演艺中心</t>
   </si>
   <si>
-    <t>摇滚巨星</t>
-  </si>
-  <si>
     <t>ROCK STAR</t>
   </si>
   <si>
@@ -203,9 +194,6 @@
   </si>
   <si>
     <t>五月天</t>
-  </si>
-  <si>
-    <t>就是演唱会 2016</t>
   </si>
   <si>
     <t>Just Rock It 2016</t>
@@ -1268,68 +1256,68 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="G2" s="5">
         <v>2026</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="5">
         <v>2026</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="G4" s="5">
         <v>2025</v>
@@ -1340,22 +1328,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="G5" s="5">
         <v>2025</v>
@@ -1366,48 +1354,48 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="G6" s="5">
         <v>2025</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="G7" s="5">
         <v>2024</v>
@@ -1421,19 +1409,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="G8" s="5">
         <v>2023</v>
@@ -1444,22 +1432,22 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="G9" s="5">
         <v>2016</v>
@@ -1470,28 +1458,28 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="G10" s="5">
         <v>2016</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1555,15 +1543,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B2" s="2" cm="1">
         <f t="array" ref="B2">COUNTA(_xlfn.UNIQUE(列表!E2:E11))</f>
@@ -1572,7 +1560,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2" cm="1">
         <f t="array" ref="B3">COUNTA(_xlfn.UNIQUE(列表!A2:A10))</f>
@@ -1581,7 +1569,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2">
         <f>COUNT(列表!G:G)</f>
@@ -1590,7 +1578,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2" cm="1">
         <f t="array" ref="B5">COUNTA(_xlfn.UNIQUE(列表!G2:G12))</f>

--- a/演唱会列表.xlsx
+++ b/演唱会列表.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="70">
   <si>
     <t>歌手</t>
   </si>
@@ -76,6 +76,9 @@
     <t>时间月</t>
   </si>
   <si>
+    <t>主题</t>
+  </si>
+  <si>
     <t>伍佰</t>
   </si>
   <si>
@@ -94,6 +97,105 @@
     <t>01</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">伍佰宣告演唱会以 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“怎么酷怎么排”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">​ 为最高准则，展开一场反套路的摇滚美学实验。他强调 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“这是我们的演唱会，不是我的演唱会”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，将歌迷视为 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“特别来宾”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">。演出融合铜管乐、电子音效与现代舞，对经典曲目进行全新改编，旨在打造跨越代际的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“万人KTV”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​ 现场。</t>
+    </r>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
     <t>李荣浩</t>
   </si>
   <si>
@@ -112,6 +214,39 @@
     <t>清远体育中心体育场</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">主题源自其第八张创作专辑《黑马》，旨在传递 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“黑马不是不合群，是听天不由命，我们每个人都是一匹黑马”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​ 的精神。舞台中心矗立巨型黑马艺术装置，整场演出是一场关于坚持、梦想与自我突破的音乐叙事，旨在唤醒每个人心中的潜能。</t>
+    </r>
+  </si>
+  <si>
     <t>邓紫棋</t>
   </si>
   <si>
@@ -127,6 +262,9 @@
     <t>广西体育中心体育场</t>
   </si>
   <si>
+    <t>“I AM GLORIA”是邓紫棋暌违六年举办的巡演。她表示，在这六年间世界发生了巨大变化，肆虐的疫情、接二连三的他国战争以及各种天灾人祸，导致许多人都像行走在荒漠里，在迷惘中渴望着驱散黑暗的曙光。邓紫棋希望可以通过歌声诉说自己经历孤独黑暗、渴望光明和自我救赎的过程，用音乐激荡人们的心灵。</t>
+  </si>
+  <si>
     <t>周传雄</t>
   </si>
   <si>
@@ -136,6 +274,81 @@
     <t>Unforgettable・Reunion</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">主题寓意 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“念念不忘，必有回响”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">。这是周传雄的首轮大型体育场巡演，旨在以 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“庆典”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​ 为核心概念，与歌迷进行一场盛大的重逢。演唱会带领观众在《黄昏》、《寂寞沙洲冷》等时代金曲中，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>与曾经的自己温柔相拥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，重温青春记忆。</t>
+    </r>
+  </si>
+  <si>
     <t>孙燕姿</t>
   </si>
   <si>
@@ -154,13 +367,16 @@
     <t>05</t>
   </si>
   <si>
+    <t>孙燕姿表示，既然“日落以前没能相聚”，那就“日落以后极美欢庆”。此次巡演的主题旨在“把生命中的每个日落串起”，深层含义为“日落之前的灿烂，日落之后的勇气，一切都值得从零开始”，孙燕姿也希望通过该巡演可以与听众再次创造美好的记忆。</t>
+  </si>
+  <si>
     <t>任贤齐</t>
   </si>
   <si>
     <t>齐迹 2024</t>
   </si>
   <si>
-    <t>Miracle 2024</t>
+    <t>Richie Jen Live 2024</t>
   </si>
   <si>
     <t>佛山</t>
@@ -169,6 +385,60 @@
     <t>佛山国际体育文化演艺中心</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">​ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“齐迹 2024”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​ 不仅是一场演唱会，更是一次以</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>任贤齐的音乐足迹为线索，汇聚集体记忆、创造共鸣奇迹的温暖旅程</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。它是对歌手个人生涯的礼赞，更是对一代人青春的回响与致敬。</t>
+    </r>
+  </si>
+  <si>
     <t>ROCK STAR</t>
   </si>
   <si>
@@ -181,6 +451,9 @@
     <t>南京奥体中心体育馆</t>
   </si>
   <si>
+    <t>“Rock Star”系列巡演的首轮，旨在重新开启观众对摇滚乐的视野与认知。伍佰宣称 “我唱的不是情歌，是人生”，演唱会横跨历年专辑的曲目，展现其音乐风格的转变与作为摇滚巨星的核心力量。</t>
+  </si>
+  <si>
     <t>陈奕迅</t>
   </si>
   <si>
@@ -193,6 +466,9 @@
     <t>国家体育场鸟巢</t>
   </si>
   <si>
+    <t>主题围绕 “LIFE”（生活），陈奕迅亲自从数百首作品中挑选与生命相关的歌曲，希望观众能 用心感受及体会生命中发生的每件小事之影响力及重要性，并投放多一些情怀发掘人生不同的意义。</t>
+  </si>
+  <si>
     <t>五月天</t>
   </si>
   <si>
@@ -209,6 +485,9 @@
   </si>
   <si>
     <t>09</t>
+  </si>
+  <si>
+    <t>演唱会以“生老病死就是一场人生派对”为主题，鼓励观众正面迎战。2016年巡演以高成本打造炫目舞台，并融入当时新专辑《自传》的概念，是一场充满能量、情怀与万人集体狂欢的摇滚派对。</t>
   </si>
   <si>
     <t>分类</t>
@@ -872,7 +1151,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -890,12 +1169,21 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1208,8 +1496,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.4444444444444" style="4" customWidth="1"/>
     <col min="2" max="2" width="25.2222222222222" style="4" customWidth="1"/>
@@ -1219,105 +1507,120 @@
     <col min="6" max="6" width="28.8888888888889" style="2" customWidth="1"/>
     <col min="7" max="7" width="9" style="5" customWidth="1"/>
     <col min="8" max="8" width="9" style="5"/>
-    <col min="9" max="9" width="15.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="33.4444444444444" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:8">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="15.6" spans="1:10">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="115.2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="5">
         <v>2026</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="100.8" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3" s="5">
         <v>2026</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="144" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" s="5">
         <v>2025</v>
@@ -1325,25 +1628,31 @@
       <c r="H4" s="5">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="100.8" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G5" s="5">
         <v>2025</v>
@@ -1351,51 +1660,63 @@
       <c r="H5" s="5">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="115.2" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G6" s="5">
         <v>2025</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>39</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="86.4" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G7" s="5">
         <v>2024</v>
@@ -1403,25 +1724,31 @@
       <c r="H7" s="5">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" ht="86.4" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G8" s="5">
         <v>2023</v>
@@ -1429,25 +1756,31 @@
       <c r="H8" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="86.4" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G9" s="5">
         <v>2016</v>
@@ -1455,64 +1788,76 @@
       <c r="H9" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="86.4" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G10" s="5">
         <v>2016</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>62</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:10">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:10">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:10">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:10">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:10">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1543,15 +1888,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B2" s="2" cm="1">
         <f t="array" ref="B2">COUNTA(_xlfn.UNIQUE(列表!E2:E11))</f>
@@ -1560,7 +1905,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B3" s="2" cm="1">
         <f t="array" ref="B3">COUNTA(_xlfn.UNIQUE(列表!A2:A10))</f>
@@ -1569,7 +1914,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B4" s="2">
         <f>COUNT(列表!G:G)</f>
@@ -1578,7 +1923,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B5" s="2" cm="1">
         <f t="array" ref="B5">COUNTA(_xlfn.UNIQUE(列表!G2:G12))</f>

--- a/演唱会列表.xlsx
+++ b/演唱会列表.xlsx
@@ -9,7 +9,19 @@
   <sheets>
     <sheet name="列表" sheetId="1" r:id="rId1"/>
     <sheet name="统计" sheetId="2" r:id="rId2"/>
+    <sheet name="五月天2016" sheetId="3" r:id="rId3"/>
+    <sheet name="陈奕迅2016" sheetId="4" r:id="rId4"/>
+    <sheet name="伍佰2023" sheetId="5" r:id="rId5"/>
+    <sheet name="任贤齐2024" sheetId="6" r:id="rId6"/>
+    <sheet name="孙燕姿2025" sheetId="7" r:id="rId7"/>
+    <sheet name="周传雄2025" sheetId="8" r:id="rId8"/>
+    <sheet name="邓紫棋2025" sheetId="9" r:id="rId9"/>
+    <sheet name="李荣浩2026" sheetId="10" r:id="rId10"/>
+    <sheet name="伍佰2026" sheetId="11" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">五月天2016!$A$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -50,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="398">
   <si>
     <t>歌手</t>
   </si>
@@ -506,6 +518,990 @@
   </si>
   <si>
     <t>年份总数</t>
+  </si>
+  <si>
+    <t>五月天歌单</t>
+  </si>
+  <si>
+    <t>Do You Ever Shine?</t>
+  </si>
+  <si>
+    <t>三个傻瓜</t>
+  </si>
+  <si>
+    <t>你不是真正的快乐</t>
+  </si>
+  <si>
+    <t>为爱而生</t>
+  </si>
+  <si>
+    <t>孙悟空</t>
+  </si>
+  <si>
+    <t>雌雄同体</t>
+  </si>
+  <si>
+    <t>人生海海</t>
+  </si>
+  <si>
+    <t>终结孤单</t>
+  </si>
+  <si>
+    <t>轧车</t>
+  </si>
+  <si>
+    <t>离开地球表面</t>
+  </si>
+  <si>
+    <t>诺亚方舟</t>
+  </si>
+  <si>
+    <t>知足</t>
+  </si>
+  <si>
+    <t>疯狂世界</t>
+  </si>
+  <si>
+    <t>笑忘歌</t>
+  </si>
+  <si>
+    <t>如烟</t>
+  </si>
+  <si>
+    <t>好好 (想把你写成一首歌)</t>
+  </si>
+  <si>
+    <t>干杯</t>
+  </si>
+  <si>
+    <t>怪兽solo + 将军令</t>
+  </si>
+  <si>
+    <t>入阵曲</t>
+  </si>
+  <si>
+    <t>我不愿让你一个人</t>
+  </si>
+  <si>
+    <t>憨人</t>
+  </si>
+  <si>
+    <t>任意门</t>
+  </si>
+  <si>
+    <t>倔强</t>
+  </si>
+  <si>
+    <t>派对动物</t>
+  </si>
+  <si>
+    <t>伤心的人别听慢歌 (贯彻快乐)</t>
+  </si>
+  <si>
+    <t>如果我们不曾相遇</t>
+  </si>
+  <si>
+    <t>温柔</t>
+  </si>
+  <si>
+    <t>后来的我们</t>
+  </si>
+  <si>
+    <t>突然好想你</t>
+  </si>
+  <si>
+    <t>OAOA</t>
+  </si>
+  <si>
+    <t>顽固</t>
+  </si>
+  <si>
+    <t>恋爱ING</t>
+  </si>
+  <si>
+    <t>陈奕迅歌单</t>
+  </si>
+  <si>
+    <t>变色龙</t>
+  </si>
+  <si>
+    <t>闪</t>
+  </si>
+  <si>
+    <t>我们都寂寞</t>
+  </si>
+  <si>
+    <t>浮城</t>
+  </si>
+  <si>
+    <t>娱乐天空</t>
+  </si>
+  <si>
+    <t>早开的长途班</t>
+  </si>
+  <si>
+    <t>淘汰</t>
+  </si>
+  <si>
+    <t>不如不见</t>
+  </si>
+  <si>
+    <t>陀飞轮</t>
+  </si>
+  <si>
+    <t>不如承诺来的简单</t>
+  </si>
+  <si>
+    <t>浮夸</t>
+  </si>
+  <si>
+    <t>2001太空漫游</t>
+  </si>
+  <si>
+    <t>无人之境</t>
+  </si>
+  <si>
+    <t>乐园</t>
+  </si>
+  <si>
+    <t>大人</t>
+  </si>
+  <si>
+    <t>碌卡</t>
+  </si>
+  <si>
+    <t>谢谢侬</t>
+  </si>
+  <si>
+    <t>多少</t>
+  </si>
+  <si>
+    <t>可以了</t>
+  </si>
+  <si>
+    <t>富士山下</t>
+  </si>
+  <si>
+    <t>沙龙</t>
+  </si>
+  <si>
+    <t>时代巨轮</t>
+  </si>
+  <si>
+    <t>结束开始</t>
+  </si>
+  <si>
+    <t>怕死</t>
+  </si>
+  <si>
+    <t>夕阳无限好</t>
+  </si>
+  <si>
+    <t>今日</t>
+  </si>
+  <si>
+    <t>我的快乐时代</t>
+  </si>
+  <si>
+    <t>明年今日</t>
+  </si>
+  <si>
+    <t>无条件</t>
+  </si>
+  <si>
+    <t>路一直都在</t>
+  </si>
+  <si>
+    <t>安可环节特别曲目（根据最终场报道）：</t>
+  </si>
+  <si>
+    <t>I DO</t>
+  </si>
+  <si>
+    <t>不要说话</t>
+  </si>
+  <si>
+    <t>夜空中最亮的星</t>
+  </si>
+  <si>
+    <t>十年</t>
+  </si>
+  <si>
+    <t>兄妹</t>
+  </si>
+  <si>
+    <t>不如这样</t>
+  </si>
+  <si>
+    <t>春夏秋冬</t>
+  </si>
+  <si>
+    <t>你给我听好</t>
+  </si>
+  <si>
+    <t>重口味</t>
+  </si>
+  <si>
+    <t>打回原形</t>
+  </si>
+  <si>
+    <t>伍佰歌单</t>
+  </si>
+  <si>
+    <t>突然的自我</t>
+  </si>
+  <si>
+    <t>挪威的森林</t>
+  </si>
+  <si>
+    <t>浪人情歌</t>
+  </si>
+  <si>
+    <t>如果这都不算爱</t>
+  </si>
+  <si>
+    <t>梦醒时分</t>
+  </si>
+  <si>
+    <t>Last Dance</t>
+  </si>
+  <si>
+    <t>再度重相逢</t>
+  </si>
+  <si>
+    <t>爱你一万年</t>
+  </si>
+  <si>
+    <t>世界第一等</t>
+  </si>
+  <si>
+    <t>我会好好的</t>
+  </si>
+  <si>
+    <t>泪桥</t>
+  </si>
+  <si>
+    <t>牵挂</t>
+  </si>
+  <si>
+    <t>被动</t>
+  </si>
+  <si>
+    <t>与你到永久</t>
+  </si>
+  <si>
+    <t>晚风</t>
+  </si>
+  <si>
+    <t>你是我的花朵</t>
+  </si>
+  <si>
+    <t>夏夜晚风</t>
+  </si>
+  <si>
+    <t>爱情的尽头</t>
+  </si>
+  <si>
+    <t>背叛</t>
+  </si>
+  <si>
+    <t>黄色月亮</t>
+  </si>
+  <si>
+    <t>原本当初</t>
+  </si>
+  <si>
+    <t>皇后的高跟鞋</t>
+  </si>
+  <si>
+    <t>亲爱的你</t>
+  </si>
+  <si>
+    <t>让水倒流</t>
+  </si>
+  <si>
+    <t>钉子花</t>
+  </si>
+  <si>
+    <t>流星</t>
+  </si>
+  <si>
+    <t>一生最爱的人</t>
+  </si>
+  <si>
+    <t>一亲红颜</t>
+  </si>
+  <si>
+    <t>就是因为爱</t>
+  </si>
+  <si>
+    <t>痛哭的人</t>
+  </si>
+  <si>
+    <t>海浪</t>
+  </si>
+  <si>
+    <t>任贤齐歌单</t>
+  </si>
+  <si>
+    <t>心太软</t>
+  </si>
+  <si>
+    <t>伤心太平洋</t>
+  </si>
+  <si>
+    <t>对面的女孩看过来</t>
+  </si>
+  <si>
+    <t>浪花一朵朵</t>
+  </si>
+  <si>
+    <t>天涯</t>
+  </si>
+  <si>
+    <t>我是一只鱼</t>
+  </si>
+  <si>
+    <t>任逍遥</t>
+  </si>
+  <si>
+    <t>春天花会开</t>
+  </si>
+  <si>
+    <t>只爱你一个人</t>
+  </si>
+  <si>
+    <t>依靠</t>
+  </si>
+  <si>
+    <t>很受伤</t>
+  </si>
+  <si>
+    <t>天使也一样</t>
+  </si>
+  <si>
+    <t>流着泪的你的脸</t>
+  </si>
+  <si>
+    <t>兄弟</t>
+  </si>
+  <si>
+    <t>花好月圆夜（与杨千嬅合唱版）</t>
+  </si>
+  <si>
+    <t>其他常演曲目：</t>
+  </si>
+  <si>
+    <t>有梦的人</t>
+  </si>
+  <si>
+    <t>一念关山（电视剧主题曲）</t>
+  </si>
+  <si>
+    <t>想你啦</t>
+  </si>
+  <si>
+    <t>你是我老婆</t>
+  </si>
+  <si>
+    <t>漂洋过海来看你</t>
+  </si>
+  <si>
+    <t>给你幸福</t>
+  </si>
+  <si>
+    <t>还有我</t>
+  </si>
+  <si>
+    <t>星语心愿</t>
+  </si>
+  <si>
+    <t>烛光</t>
+  </si>
+  <si>
+    <t>爱江山更爱美人</t>
+  </si>
+  <si>
+    <t>沧海一声笑</t>
+  </si>
+  <si>
+    <t>花太香</t>
+  </si>
+  <si>
+    <t>爱的路上只有我和你</t>
+  </si>
+  <si>
+    <t>橘子香水</t>
+  </si>
+  <si>
+    <t>死不了</t>
+  </si>
+  <si>
+    <t>哭个痛快</t>
+  </si>
+  <si>
+    <t>诛仙我回来</t>
+  </si>
+  <si>
+    <t>在路上</t>
+  </si>
+  <si>
+    <t>任性</t>
+  </si>
+  <si>
+    <t>特别曲目（根据场次可能有所不同）：</t>
+  </si>
+  <si>
+    <t>男儿当自强（翻唱）</t>
+  </si>
+  <si>
+    <t>一生何求（翻唱）</t>
+  </si>
+  <si>
+    <t>让一切随风（翻唱）</t>
+  </si>
+  <si>
+    <t>海阔天空（最终场安可曲目，据抖音视频显示）</t>
+  </si>
+  <si>
+    <t>孙燕姿歌单</t>
+  </si>
+  <si>
+    <t>开场及快歌部分：</t>
+  </si>
+  <si>
+    <t>极美（Intro）</t>
+  </si>
+  <si>
+    <t>我要的幸福</t>
+  </si>
+  <si>
+    <t>超快感</t>
+  </si>
+  <si>
+    <t>绿光</t>
+  </si>
+  <si>
+    <t>神奇</t>
+  </si>
+  <si>
+    <t>经典慢歌部分：</t>
+  </si>
+  <si>
+    <t>我的爱 + 我不爱</t>
+  </si>
+  <si>
+    <t>我不难过</t>
+  </si>
+  <si>
+    <t>隐形人</t>
+  </si>
+  <si>
+    <t>奔</t>
+  </si>
+  <si>
+    <t>风筝</t>
+  </si>
+  <si>
+    <t>逃亡</t>
+  </si>
+  <si>
+    <t>完美的一天</t>
+  </si>
+  <si>
+    <t>The Moment</t>
+  </si>
+  <si>
+    <t>遇见</t>
+  </si>
+  <si>
+    <t>我怀念的</t>
+  </si>
+  <si>
+    <t>平日快乐</t>
+  </si>
+  <si>
+    <t>第一天</t>
+  </si>
+  <si>
+    <t>逆光</t>
+  </si>
+  <si>
+    <t>天黑黑</t>
+  </si>
+  <si>
+    <t>Stefanie</t>
+  </si>
+  <si>
+    <t>其他曲目（根据VCR和点歌环节）：</t>
+  </si>
+  <si>
+    <t>彩虹金刚（VCR背景音乐）</t>
+  </si>
+  <si>
+    <t>随堂测验</t>
+  </si>
+  <si>
+    <t>真的</t>
+  </si>
+  <si>
+    <t>祝你开心</t>
+  </si>
+  <si>
+    <t>克卜勒</t>
+  </si>
+  <si>
+    <t>没有人的方向</t>
+  </si>
+  <si>
+    <t>点歌环节特别曲目（根据现场观众点歌）：</t>
+  </si>
+  <si>
+    <t>一样的夏天</t>
+  </si>
+  <si>
+    <t>雨天</t>
+  </si>
+  <si>
+    <t>当冬夜渐暖</t>
+  </si>
+  <si>
+    <t>爱情证书</t>
+  </si>
+  <si>
+    <t>漩涡</t>
+  </si>
+  <si>
+    <t>我也很想他（可能）</t>
+  </si>
+  <si>
+    <t>周传雄歌单</t>
+  </si>
+  <si>
+    <t>开场及经典曲目：</t>
+  </si>
+  <si>
+    <t>春神曲</t>
+  </si>
+  <si>
+    <t>花香</t>
+  </si>
+  <si>
+    <t>蓝色土耳其</t>
+  </si>
+  <si>
+    <t>黄粱梦</t>
+  </si>
+  <si>
+    <t>记事本</t>
+  </si>
+  <si>
+    <t>弱水三千</t>
+  </si>
+  <si>
+    <t>孤单的习惯</t>
+  </si>
+  <si>
+    <t>今宵酒醒何处</t>
+  </si>
+  <si>
+    <t>我该怎么爱你</t>
+  </si>
+  <si>
+    <t>我的心太乱</t>
+  </si>
+  <si>
+    <t>关不上的窗</t>
+  </si>
+  <si>
+    <t>哈萨雅琪</t>
+  </si>
+  <si>
+    <t>You Should Try</t>
+  </si>
+  <si>
+    <t>再出发</t>
+  </si>
+  <si>
+    <t>哈啰</t>
+  </si>
+  <si>
+    <t>滴滴滴滴</t>
+  </si>
+  <si>
+    <t>暖风</t>
+  </si>
+  <si>
+    <t>伤痛无声</t>
+  </si>
+  <si>
+    <t>幸福的瞬间</t>
+  </si>
+  <si>
+    <t>末班车/存在</t>
+  </si>
+  <si>
+    <t>情人该有的慈悲</t>
+  </si>
+  <si>
+    <t>男人海洋</t>
+  </si>
+  <si>
+    <t>我在身边</t>
+  </si>
+  <si>
+    <t>给你的歌</t>
+  </si>
+  <si>
+    <t>出卖</t>
+  </si>
+  <si>
+    <t>冬天的秘密</t>
+  </si>
+  <si>
+    <t>我难过</t>
+  </si>
+  <si>
+    <t>快乐练习曲</t>
+  </si>
+  <si>
+    <t>忘记</t>
+  </si>
+  <si>
+    <t>再见北极雪</t>
+  </si>
+  <si>
+    <t>寂寞边界</t>
+  </si>
+  <si>
+    <t>青花</t>
+  </si>
+  <si>
+    <t>黄昏</t>
+  </si>
+  <si>
+    <t>有没有一首歌会让你想起我</t>
+  </si>
+  <si>
+    <t>寂寞沙洲冷</t>
+  </si>
+  <si>
+    <t>花车巡场环节特别曲目（根据官方回顾）：</t>
+  </si>
+  <si>
+    <t>邓紫棋歌单</t>
+  </si>
+  <si>
+    <t>摩天动物园</t>
+  </si>
+  <si>
+    <t>灰狼</t>
+  </si>
+  <si>
+    <t>来自天堂的魔鬼</t>
+  </si>
+  <si>
+    <t>光年之外</t>
+  </si>
+  <si>
+    <t>差不多姑娘</t>
+  </si>
+  <si>
+    <t>透明</t>
+  </si>
+  <si>
+    <t>HELL（地狱）</t>
+  </si>
+  <si>
+    <t>孤独</t>
+  </si>
+  <si>
+    <t>经典情歌及抒情曲目：</t>
+  </si>
+  <si>
+    <t>冰河时代</t>
+  </si>
+  <si>
+    <t>于是</t>
+  </si>
+  <si>
+    <t>再见</t>
+  </si>
+  <si>
+    <t>你不是第一个离开的人</t>
+  </si>
+  <si>
+    <t>睡公主</t>
+  </si>
+  <si>
+    <t>A.I.N.Y.（爱你）</t>
+  </si>
+  <si>
+    <t>Where Did U Go（你去了哪里）</t>
+  </si>
+  <si>
+    <t>存在</t>
+  </si>
+  <si>
+    <t>你把我灌醉</t>
+  </si>
+  <si>
+    <t>红蔷薇白玫瑰</t>
+  </si>
+  <si>
+    <t>唯一</t>
+  </si>
+  <si>
+    <t>句号</t>
+  </si>
+  <si>
+    <t>GLORIA（歌莉雅）</t>
+  </si>
+  <si>
+    <t>You Raise Me Up（你鼓舞了我）</t>
+  </si>
+  <si>
+    <t>让世界暂停一分钟</t>
+  </si>
+  <si>
+    <t>老人与海</t>
+  </si>
+  <si>
+    <t>多远都要在一起</t>
+  </si>
+  <si>
+    <t>FIND YOU（找到你）</t>
+  </si>
+  <si>
+    <t>喜欢你</t>
+  </si>
+  <si>
+    <t>夜的尽头</t>
+  </si>
+  <si>
+    <t>倒数</t>
+  </si>
+  <si>
+    <t>新的心跳</t>
+  </si>
+  <si>
+    <t>泡沫</t>
+  </si>
+  <si>
+    <t>我的秘密</t>
+  </si>
+  <si>
+    <t>回忆的沙漏</t>
+  </si>
+  <si>
+    <t>少年与海</t>
+  </si>
+  <si>
+    <t>其他可能曲目（根据不同场次调整）：</t>
+  </si>
+  <si>
+    <t>海阔天空</t>
+  </si>
+  <si>
+    <t>天空没有极限</t>
+  </si>
+  <si>
+    <t>情人</t>
+  </si>
+  <si>
+    <t>平凡天使</t>
+  </si>
+  <si>
+    <t>不想回家</t>
+  </si>
+  <si>
+    <t>后会无期</t>
+  </si>
+  <si>
+    <t>画</t>
+  </si>
+  <si>
+    <t>受难曲</t>
+  </si>
+  <si>
+    <t>龙卷风</t>
+  </si>
+  <si>
+    <t>李荣浩歌单</t>
+  </si>
+  <si>
+    <t>开场及新专辑曲目：</t>
+  </si>
+  <si>
+    <t>黑马（主题曲）</t>
+  </si>
+  <si>
+    <t>快让我在雪地上撒点儿野</t>
+  </si>
+  <si>
+    <t>嗯</t>
+  </si>
+  <si>
+    <t>走走</t>
+  </si>
+  <si>
+    <t>鸿门宴</t>
+  </si>
+  <si>
+    <t>海陆风</t>
+  </si>
+  <si>
+    <t>一百</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>经典热门曲目：</t>
+  </si>
+  <si>
+    <t>乌梅子酱</t>
+  </si>
+  <si>
+    <t>戒烟</t>
+  </si>
+  <si>
+    <t>李白</t>
+  </si>
+  <si>
+    <t>模特</t>
+  </si>
+  <si>
+    <t>年少有为</t>
+  </si>
+  <si>
+    <t>不将就</t>
+  </si>
+  <si>
+    <t>麻雀</t>
+  </si>
+  <si>
+    <t>爸爸妈妈</t>
+  </si>
+  <si>
+    <t>老街</t>
+  </si>
+  <si>
+    <t>喜剧之王</t>
+  </si>
+  <si>
+    <t>作曲家</t>
+  </si>
+  <si>
+    <t>太坦白</t>
+  </si>
+  <si>
+    <t>耳朵</t>
+  </si>
+  <si>
+    <t>不说</t>
+  </si>
+  <si>
+    <t>不遗憾</t>
+  </si>
+  <si>
+    <t>等着等着就老了</t>
+  </si>
+  <si>
+    <t>都一样</t>
+  </si>
+  <si>
+    <t>恋人</t>
+  </si>
+  <si>
+    <t>为他人创作的"浩式情歌"（亲自演绎）：</t>
+  </si>
+  <si>
+    <t>拿走了什么（原唱：A-Lin）</t>
+  </si>
+  <si>
+    <t>慢慢喜欢你（原唱：莫文蔚）</t>
+  </si>
+  <si>
+    <t>丑八怪（原唱：薛之谦）</t>
+  </si>
+  <si>
+    <t>不再见（原唱：陈学冬）</t>
+  </si>
+  <si>
+    <t>女儿国（原唱：张靓颖）</t>
+  </si>
+  <si>
+    <t>其他曲目（根据场次可能有所不同）：</t>
+  </si>
+  <si>
+    <t>慢冷</t>
+  </si>
+  <si>
+    <t>落俗</t>
+  </si>
+  <si>
+    <t>乐团</t>
+  </si>
+  <si>
+    <t>歌谣</t>
+  </si>
+  <si>
+    <t>紫荆花盛开</t>
+  </si>
+  <si>
+    <t>脱胎换骨</t>
+  </si>
+  <si>
+    <t>假面</t>
+  </si>
+  <si>
+    <t>特别嘉宾环节（1月2日场）：</t>
+  </si>
+  <si>
+    <t>Made Me a Man（与王嘉尔合作）</t>
+  </si>
+  <si>
+    <t>翅膀</t>
+  </si>
+  <si>
+    <t>冲冲冲</t>
+  </si>
+  <si>
+    <t>坚强的理由</t>
+  </si>
+  <si>
+    <t>爱拼才会赢</t>
+  </si>
+  <si>
+    <t>爱情限时批</t>
+  </si>
+  <si>
+    <t>白鸽</t>
+  </si>
+  <si>
+    <t>上瘾了</t>
+  </si>
+  <si>
+    <t>最想你的</t>
+  </si>
+  <si>
+    <t>我是老大</t>
+  </si>
+  <si>
+    <t>一点点</t>
+  </si>
+  <si>
+    <t>风火</t>
+  </si>
+  <si>
+    <t>心爱的再会啦</t>
+  </si>
+  <si>
+    <t>彩虹</t>
+  </si>
+  <si>
+    <t>怎样歌</t>
   </si>
 </sst>
 </file>
@@ -1151,8 +2147,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1499,72 +2519,72 @@
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.4444444444444" style="4" customWidth="1"/>
-    <col min="2" max="2" width="25.2222222222222" style="4" customWidth="1"/>
-    <col min="3" max="3" width="26.7777777777778" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.6666666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14.1111111111111" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.8888888888889" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9" style="5" customWidth="1"/>
-    <col min="8" max="8" width="9" style="5"/>
-    <col min="9" max="9" width="33.4444444444444" style="6" customWidth="1"/>
+    <col min="1" max="1" width="11.4444444444444" style="12" customWidth="1"/>
+    <col min="2" max="2" width="25.2222222222222" style="12" customWidth="1"/>
+    <col min="3" max="3" width="26.7777777777778" style="12" customWidth="1"/>
+    <col min="4" max="4" width="12.6666666666667" style="12" customWidth="1"/>
+    <col min="5" max="5" width="14.1111111111111" style="10" customWidth="1"/>
+    <col min="6" max="6" width="28.8888888888889" style="10" customWidth="1"/>
+    <col min="7" max="7" width="9" style="13" customWidth="1"/>
+    <col min="8" max="8" width="9" style="13"/>
+    <col min="9" max="9" width="33.4444444444444" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" spans="1:10">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="115.2" spans="1:10">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="13">
         <v>2026</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="17" t="s">
         <v>15</v>
       </c>
       <c r="J2" t="s">
@@ -1572,31 +2592,31 @@
       </c>
     </row>
     <row r="3" ht="100.8" spans="1:10">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="13">
         <v>2026</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="14" t="s">
         <v>23</v>
       </c>
       <c r="J3" t="s">
@@ -1604,31 +2624,31 @@
       </c>
     </row>
     <row r="4" ht="144" spans="1:10">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="13">
         <v>2025</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="13">
         <v>11</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="18" t="s">
         <v>29</v>
       </c>
       <c r="J4" t="s">
@@ -1636,31 +2656,31 @@
       </c>
     </row>
     <row r="5" ht="100.8" spans="1:10">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="13">
         <v>2025</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="13">
         <v>11</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="17" t="s">
         <v>33</v>
       </c>
       <c r="J5" t="s">
@@ -1668,31 +2688,31 @@
       </c>
     </row>
     <row r="6" ht="115.2" spans="1:10">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="13">
         <v>2025</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="14" t="s">
         <v>40</v>
       </c>
       <c r="J6" t="s">
@@ -1700,31 +2720,31 @@
       </c>
     </row>
     <row r="7" ht="86.4" spans="1:10">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="13">
         <v>2024</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="13">
         <v>12</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="14" t="s">
         <v>46</v>
       </c>
       <c r="J7" t="s">
@@ -1732,31 +2752,31 @@
       </c>
     </row>
     <row r="8" ht="86.4" spans="1:10">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="13">
         <v>2023</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="13">
         <v>10</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="14" t="s">
         <v>51</v>
       </c>
       <c r="J8" t="s">
@@ -1764,31 +2784,31 @@
       </c>
     </row>
     <row r="9" ht="86.4" spans="1:10">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="13">
         <v>2016</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="13">
         <v>10</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="14" t="s">
         <v>56</v>
       </c>
       <c r="J9" t="s">
@@ -1796,31 +2816,31 @@
       </c>
     </row>
     <row r="10" ht="86.4" spans="1:10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="13">
         <v>2016</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="14" t="s">
         <v>63</v>
       </c>
       <c r="J10" t="s">
@@ -1828,50 +2848,470 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A45"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="43.5555555555556" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="5" t="s">
+        <v>383</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A33"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14.1111111111111" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1882,50 +3322,50 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.4444444444444" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.4444444444444" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="2" cm="1">
+      <c r="B2" s="10" cm="1">
         <f t="array" ref="B2">COUNTA(_xlfn.UNIQUE(列表!E2:E11))</f>
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="2" cm="1">
+      <c r="B3" s="10" cm="1">
         <f t="array" ref="B3">COUNTA(_xlfn.UNIQUE(列表!A2:A10))</f>
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="10">
         <f>COUNT(列表!G:G)</f>
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="2" cm="1">
+      <c r="B5" s="10" cm="1">
         <f t="array" ref="B5">COUNTA(_xlfn.UNIQUE(列表!G2:G12))</f>
         <v>5</v>
       </c>
@@ -1935,4 +3375,1489 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A33"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="32" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A42"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.7777777777778" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A32"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16.4444444444444" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="50.4444444444444" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A37"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="45.7777777777778" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A43"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="21.7777777777778" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A48"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="41" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/演唱会列表.xlsx
+++ b/演唱会列表.xlsx
@@ -16,9 +16,10 @@
     <sheet name="孙燕姿2025" sheetId="7" r:id="rId7"/>
     <sheet name="周传雄2025" sheetId="8" r:id="rId8"/>
     <sheet name="邓紫棋2025" sheetId="9" r:id="rId9"/>
-    <sheet name="李荣浩2026" sheetId="10" r:id="rId10"/>
+    <sheet name="李荣浩202601" sheetId="10" r:id="rId10"/>
     <sheet name="伍佰2026" sheetId="11" r:id="rId11"/>
     <sheet name="周杰伦2026" sheetId="12" r:id="rId12"/>
+    <sheet name="蔡依林202605" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">五月天2016!$A$1</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="506">
   <si>
     <t>歌手</t>
   </si>
@@ -522,6 +523,18 @@
     <t>2026年巡演首创"一城一名"定制模式，每座城市均以周董歌名或专辑定调，打造不可复制的仪式感。南宁站定名为"甜甜的"，既源自《甜甜的》那首轻快俏皮的经典情歌，更与这座城市的气质不谋而合，青秀山的清风、南湖的波光、老街的糖水铺，处处透着温润与甘甜。"甜甜的"不只是一首歌，更是一种城市情绪：是南宁街头的果香四溢，是夜市里的一碗糖水，是周氏情歌里那份青春的悸动与温柔。</t>
   </si>
   <si>
+    <t>蔡依林</t>
+  </si>
+  <si>
+    <t>PLEASURE 世界巡回演唱会</t>
+  </si>
+  <si>
+    <t>PLEASURE World Tour</t>
+  </si>
+  <si>
+    <t>蔡依林全新主题巡回演唱会 "PLEASURE"，以"面对内心、找到真实自我"为核心命题，打造出一座横跨音乐、视觉与感官体验的巨型舞台。整场演出围绕"一个女孩的成长故事"展开：她从童年的花园出走，穿越现实与欲望的挑战，在一次次考验中重新拥抱自己，最终找到回归内在的稳定力量。</t>
+  </si>
+  <si>
     <t>分类</t>
   </si>
   <si>
@@ -1555,6 +1568,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>串烧环节</t>
     </r>
     <r>
@@ -1645,6 +1666,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>乐队表演</t>
     </r>
     <r>
@@ -1720,6 +1749,126 @@
   </si>
   <si>
     <t>等你下课 (with 杨瑞代)</t>
+  </si>
+  <si>
+    <t>蔡依林歌单</t>
+  </si>
+  <si>
+    <t>《SEVEN》</t>
+  </si>
+  <si>
+    <t>《红衣女孩》</t>
+  </si>
+  <si>
+    <t>《美杜莎》</t>
+  </si>
+  <si>
+    <t>《DIY》</t>
+  </si>
+  <si>
+    <t>《l'm Not Yours》</t>
+  </si>
+  <si>
+    <t>《恶之必要》</t>
+  </si>
+  <si>
+    <t>《特务J》</t>
+  </si>
+  <si>
+    <t>《大艺术家》</t>
+  </si>
+  <si>
+    <t>《你也有今天》</t>
+  </si>
+  <si>
+    <t>《热冬》</t>
+  </si>
+  <si>
+    <t>《BloodyMary》</t>
+  </si>
+  <si>
+    <t>《甜秘密》</t>
+  </si>
+  <si>
+    <t>《WomansWork》</t>
+  </si>
+  <si>
+    <t>《美人计》</t>
+  </si>
+  <si>
+    <t>《FishLove》</t>
+  </si>
+  <si>
+    <t>《诗人漫步》</t>
+  </si>
+  <si>
+    <t>《妥协》</t>
+  </si>
+  <si>
+    <t>《Pillow》</t>
+  </si>
+  <si>
+    <t>《天空》</t>
+  </si>
+  <si>
+    <t>《倒带》</t>
+  </si>
+  <si>
+    <t>《假装》</t>
+  </si>
+  <si>
+    <t>《柠檬草的味道》</t>
+  </si>
+  <si>
+    <t>《消极》</t>
+  </si>
+  <si>
+    <t>《insideout》</t>
+  </si>
+  <si>
+    <t>《Safari》</t>
+  </si>
+  <si>
+    <t>《都没差》</t>
+  </si>
+  <si>
+    <t>《日不落》</t>
+  </si>
+  <si>
+    <t>《马德里不思议》</t>
+  </si>
+  <si>
+    <t>《说爱你》</t>
+  </si>
+  <si>
+    <t>《脑公》</t>
+  </si>
+  <si>
+    <t>《花蝴蝶》</t>
+  </si>
+  <si>
+    <t>《看我72变》</t>
+  </si>
+  <si>
+    <t>《Pleasure》</t>
+  </si>
+  <si>
+    <t>《爱无赦》</t>
+  </si>
+  <si>
+    <t>《怪美的》</t>
+  </si>
+  <si>
+    <t>《The Divine Comedy:Purgatorio》(Intro)</t>
+  </si>
+  <si>
+    <t>《舞娘》</t>
+  </si>
+  <si>
+    <t>《Stars Align》</t>
+  </si>
+  <si>
+    <t>《Play我呸》</t>
   </si>
 </sst>
 </file>
@@ -2365,7 +2514,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2375,19 +2524,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2734,72 +2877,72 @@
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.4444444444444" style="11" customWidth="1"/>
-    <col min="2" max="2" width="41" style="11" customWidth="1"/>
-    <col min="3" max="3" width="26.7777777777778" style="11" customWidth="1"/>
-    <col min="4" max="4" width="12.6666666666667" style="11" customWidth="1"/>
-    <col min="5" max="5" width="14.1111111111111" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.8888888888889" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9" style="12" customWidth="1"/>
-    <col min="8" max="8" width="9" style="12"/>
-    <col min="9" max="9" width="33.4444444444444" style="13" customWidth="1"/>
+    <col min="1" max="1" width="11.4444444444444" style="9" customWidth="1"/>
+    <col min="2" max="2" width="41" style="9" customWidth="1"/>
+    <col min="3" max="3" width="26.7777777777778" style="9" customWidth="1"/>
+    <col min="4" max="4" width="12.6666666666667" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.1111111111111" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28.8888888888889" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9" style="10" customWidth="1"/>
+    <col min="8" max="8" width="9" style="10"/>
+    <col min="9" max="9" width="33.4444444444444" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="86.4" spans="1:10">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="10">
         <v>2016</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="10">
         <v>10</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="11" t="s">
         <v>13</v>
       </c>
       <c r="J2" t="s">
@@ -2807,31 +2950,31 @@
       </c>
     </row>
     <row r="3" ht="86.4" spans="1:10">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="10">
         <v>2016</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="11" t="s">
         <v>21</v>
       </c>
       <c r="J3" t="s">
@@ -2839,31 +2982,31 @@
       </c>
     </row>
     <row r="4" ht="86.4" spans="1:10">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="10">
         <v>2023</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="10">
         <v>10</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="11" t="s">
         <v>27</v>
       </c>
       <c r="J4" t="s">
@@ -2871,31 +3014,31 @@
       </c>
     </row>
     <row r="5" ht="86.4" spans="1:10">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="10">
         <v>2024</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="10">
         <v>12</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="11" t="s">
         <v>34</v>
       </c>
       <c r="J5" t="s">
@@ -2903,31 +3046,31 @@
       </c>
     </row>
     <row r="6" ht="144" spans="1:10">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="10">
         <v>2025</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="10">
         <v>11</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="14" t="s">
         <v>40</v>
       </c>
       <c r="J6" t="s">
@@ -2935,31 +3078,31 @@
       </c>
     </row>
     <row r="7" ht="100.8" spans="1:10">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="10">
         <v>2025</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="10">
         <v>11</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="15" t="s">
         <v>44</v>
       </c>
       <c r="J7" t="s">
@@ -2967,31 +3110,31 @@
       </c>
     </row>
     <row r="8" ht="115.2" spans="1:10">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="10">
         <v>2025</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="11" t="s">
         <v>51</v>
       </c>
       <c r="J8" t="s">
@@ -2999,31 +3142,31 @@
       </c>
     </row>
     <row r="9" ht="115.2" spans="1:10">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="10">
         <v>2026</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="15" t="s">
         <v>57</v>
       </c>
       <c r="J9" t="s">
@@ -3031,31 +3174,31 @@
       </c>
     </row>
     <row r="10" ht="100.8" spans="1:10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="10">
         <v>2026</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="11" t="s">
         <v>63</v>
       </c>
       <c r="J10" t="s">
@@ -3063,69 +3206,92 @@
       </c>
     </row>
     <row r="11" ht="172.8" spans="1:10">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+    <row r="12" ht="129.6" spans="1:10">
+      <c r="A12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3140,232 +3306,232 @@
   <dimension ref="A1:A45"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.5555555555556" style="5" customWidth="1"/>
+    <col min="1" max="1" width="43.5555555555556" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="7" t="s">
-        <v>346</v>
+      <c r="A2" s="4" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="6" t="s">
-        <v>347</v>
+      <c r="A3" s="5" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
-        <v>348</v>
+      <c r="A4" s="5" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="6" t="s">
-        <v>349</v>
+      <c r="A5" s="5" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="6" t="s">
-        <v>350</v>
+      <c r="A6" s="5" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
-        <v>351</v>
+      <c r="A7" s="5" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="6" t="s">
-        <v>352</v>
+      <c r="A8" s="5" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="6" t="s">
-        <v>353</v>
+      <c r="A9" s="5" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
-        <v>354</v>
+      <c r="A10" s="5" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="7" t="s">
-        <v>355</v>
+      <c r="A11" s="4" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="6" t="s">
-        <v>356</v>
+      <c r="A12" s="5" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="6" t="s">
-        <v>357</v>
+      <c r="A13" s="5" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="6" t="s">
-        <v>358</v>
+      <c r="A14" s="5" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="6" t="s">
-        <v>359</v>
+      <c r="A15" s="5" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="6" t="s">
-        <v>360</v>
+      <c r="A16" s="5" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="6" t="s">
-        <v>361</v>
+      <c r="A17" s="5" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="6" t="s">
-        <v>362</v>
+      <c r="A18" s="5" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="6" t="s">
-        <v>363</v>
+      <c r="A19" s="5" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="6" t="s">
-        <v>364</v>
+      <c r="A20" s="5" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="6" t="s">
-        <v>365</v>
+      <c r="A21" s="5" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="6" t="s">
-        <v>366</v>
+      <c r="A22" s="5" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="6" t="s">
-        <v>367</v>
+      <c r="A23" s="5" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="6" t="s">
-        <v>368</v>
+      <c r="A24" s="5" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="6" t="s">
-        <v>369</v>
+      <c r="A25" s="5" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="6" t="s">
-        <v>370</v>
+      <c r="A26" s="5" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
-        <v>371</v>
+      <c r="A27" s="5" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="6" t="s">
-        <v>372</v>
+      <c r="A28" s="5" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="6" t="s">
-        <v>373</v>
+      <c r="A29" s="5" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="7" t="s">
-        <v>374</v>
+      <c r="A30" s="4" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="6" t="s">
-        <v>375</v>
+      <c r="A31" s="5" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="6" t="s">
-        <v>376</v>
+      <c r="A32" s="5" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="6" t="s">
-        <v>377</v>
+      <c r="A33" s="5" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="6" t="s">
-        <v>378</v>
+      <c r="A34" s="5" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="6" t="s">
-        <v>379</v>
+      <c r="A35" s="5" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="7" t="s">
-        <v>380</v>
+      <c r="A36" s="4" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="6" t="s">
-        <v>381</v>
+      <c r="A37" s="5" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="6" t="s">
-        <v>382</v>
+      <c r="A38" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="6" t="s">
-        <v>383</v>
+      <c r="A39" s="5" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="6" t="s">
-        <v>384</v>
+      <c r="A40" s="5" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="6" t="s">
-        <v>385</v>
+      <c r="A41" s="5" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="6" t="s">
-        <v>386</v>
+      <c r="A42" s="5" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="6" t="s">
-        <v>387</v>
+      <c r="A43" s="5" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="7" t="s">
-        <v>388</v>
+      <c r="A44" s="4" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="8" t="s">
-        <v>389</v>
+      <c r="A45" s="6" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -3380,172 +3546,172 @@
   <dimension ref="A1:A33"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1111111111111" style="5" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="6" t="s">
-        <v>390</v>
+      <c r="A2" s="5" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="6" t="s">
-        <v>167</v>
+      <c r="A3" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="5" t="s">
         <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="6" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="6" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="6" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="6" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="6" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="6" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="6" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="6" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="6" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="6" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="6" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -3560,307 +3726,527 @@
   <dimension ref="A1:A60"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="40.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.1111111111111" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
-        <v>405</v>
+      <c r="A2" s="4" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
-        <v>406</v>
+      <c r="A3" s="5" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
-        <v>407</v>
+      <c r="A4" s="5" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
-        <v>408</v>
+      <c r="A5" s="5" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
-        <v>409</v>
+      <c r="A6" s="5" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
-        <v>410</v>
+      <c r="A7" s="4" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
-        <v>411</v>
+      <c r="A8" s="5" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
-        <v>412</v>
+      <c r="A9" s="5" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
-        <v>413</v>
+      <c r="A10" s="5" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="3" t="s">
-        <v>414</v>
+      <c r="A11" s="4" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
-        <v>415</v>
+      <c r="A12" s="5" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
-        <v>416</v>
+      <c r="A13" s="5" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
-        <v>417</v>
+      <c r="A14" s="5" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
-        <v>418</v>
+      <c r="A15" s="5" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
-        <v>419</v>
+      <c r="A16" s="5" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
-        <v>420</v>
+      <c r="A17" s="5" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
-        <v>421</v>
+      <c r="A18" s="5" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
-        <v>422</v>
+      <c r="A19" s="5" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
-        <v>423</v>
+      <c r="A20" s="5" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
-        <v>424</v>
+      <c r="A21" s="5" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
-        <v>425</v>
+      <c r="A22" s="5" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
-        <v>426</v>
+      <c r="A23" s="5" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
-        <v>427</v>
+      <c r="A24" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
-        <v>428</v>
+      <c r="A25" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="3" t="s">
-        <v>429</v>
+      <c r="A26" s="4" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
-        <v>430</v>
+      <c r="A27" s="5" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
-        <v>431</v>
+      <c r="A28" s="5" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
-        <v>432</v>
+      <c r="A29" s="5" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
-        <v>344</v>
+      <c r="A30" s="5" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
-        <v>433</v>
+      <c r="A31" s="5" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
-        <v>434</v>
+      <c r="A32" s="5" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="3" t="s">
-        <v>435</v>
+      <c r="A33" s="4" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="4" t="s">
-        <v>436</v>
+      <c r="A34" s="5" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="4" t="s">
-        <v>437</v>
+      <c r="A35" s="5" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="4" t="s">
-        <v>438</v>
+      <c r="A36" s="5" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="4" t="s">
-        <v>439</v>
+      <c r="A37" s="5" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="3" t="s">
-        <v>440</v>
+      <c r="A38" s="4" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="4" t="s">
-        <v>441</v>
+      <c r="A39" s="5" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="4" t="s">
-        <v>442</v>
+      <c r="A40" s="5" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4" t="s">
-        <v>443</v>
+      <c r="A41" s="5" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="3" t="s">
-        <v>444</v>
+      <c r="A42" s="4" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="4" t="s">
-        <v>445</v>
+      <c r="A43" s="5" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="4" t="s">
-        <v>446</v>
+      <c r="A44" s="5" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="4" t="s">
-        <v>447</v>
+      <c r="A45" s="5" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="4" t="s">
-        <v>448</v>
+      <c r="A46" s="5" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="4" t="s">
-        <v>449</v>
+      <c r="A47" s="5" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="4" t="s">
-        <v>450</v>
+      <c r="A48" s="5" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="4" t="s">
-        <v>451</v>
+      <c r="A49" s="5" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="4" t="s">
-        <v>452</v>
+      <c r="A50" s="5" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="4" t="s">
-        <v>453</v>
+      <c r="A51" s="5" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="4" t="s">
-        <v>454</v>
+      <c r="A52" s="5" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="4" t="s">
-        <v>455</v>
+      <c r="A53" s="5" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="4" t="s">
-        <v>456</v>
+      <c r="A54" s="5" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="4" t="s">
-        <v>116</v>
+      <c r="A55" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="4" t="s">
-        <v>457</v>
+      <c r="A56" s="5" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="4" t="s">
-        <v>458</v>
+      <c r="A57" s="5" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="3" t="s">
-        <v>459</v>
+      <c r="A58" s="4" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="4" t="s">
-        <v>460</v>
+      <c r="A59" s="5" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="4" t="s">
-        <v>461</v>
+      <c r="A60" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="44.5555555555556" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -3876,49 +4262,49 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="17" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.4444444444444" style="5" customWidth="1"/>
+    <col min="2" max="2" width="18.4444444444444" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="5" cm="1">
+      <c r="A2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="3" cm="1">
         <f t="array" ref="B2">COUNTA(_xlfn.UNIQUE(列表!E2:E11))</f>
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="5" cm="1">
+      <c r="A3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="3" cm="1">
         <f t="array" ref="B3">COUNTA(_xlfn.UNIQUE(列表!A2:A10))</f>
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="5">
+      <c r="A4" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="3">
         <f>COUNT(列表!G:G)</f>
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="5" cm="1">
+      <c r="A5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="3" cm="1">
         <f t="array" ref="B5">COUNTA(_xlfn.UNIQUE(列表!G2:G12))</f>
         <v>6</v>
       </c>
@@ -3936,172 +4322,172 @@
   <dimension ref="A1:A33"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="32" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="6" t="s">
-        <v>77</v>
+      <c r="A2" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="6" t="s">
-        <v>78</v>
+      <c r="A3" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
-        <v>79</v>
+      <c r="A4" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="6" t="s">
-        <v>80</v>
+      <c r="A5" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="6" t="s">
-        <v>81</v>
+      <c r="A6" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
-        <v>82</v>
+      <c r="A7" s="5" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="6" t="s">
-        <v>83</v>
+      <c r="A8" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="6" t="s">
-        <v>84</v>
+      <c r="A9" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
-        <v>85</v>
+      <c r="A10" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="6" t="s">
-        <v>86</v>
+      <c r="A11" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="6" t="s">
-        <v>87</v>
+      <c r="A12" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="6" t="s">
-        <v>88</v>
+      <c r="A13" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="6" t="s">
-        <v>89</v>
+      <c r="A14" s="5" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="6" t="s">
-        <v>90</v>
+      <c r="A15" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="6" t="s">
-        <v>91</v>
+      <c r="A16" s="5" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="6" t="s">
-        <v>92</v>
+      <c r="A17" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="6" t="s">
-        <v>93</v>
+      <c r="A18" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="6" t="s">
-        <v>94</v>
+      <c r="A19" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="6" t="s">
-        <v>95</v>
+      <c r="A20" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="6" t="s">
-        <v>96</v>
+      <c r="A21" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="6" t="s">
-        <v>97</v>
+      <c r="A22" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="6" t="s">
-        <v>98</v>
+      <c r="A23" s="5" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="6" t="s">
-        <v>99</v>
+      <c r="A24" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="6" t="s">
-        <v>100</v>
+      <c r="A25" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="6" t="s">
-        <v>101</v>
+      <c r="A26" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
-        <v>102</v>
+      <c r="A27" s="5" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="6" t="s">
-        <v>103</v>
+      <c r="A28" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="6" t="s">
-        <v>104</v>
+      <c r="A29" s="5" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="6" t="s">
-        <v>105</v>
+      <c r="A30" s="5" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="6" t="s">
-        <v>106</v>
+      <c r="A31" s="5" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="6" t="s">
-        <v>107</v>
+      <c r="A32" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="6" t="s">
-        <v>108</v>
+      <c r="A33" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -4116,217 +4502,217 @@
   <dimension ref="A1:A42"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.7777777777778" style="5" customWidth="1"/>
+    <col min="1" max="1" width="12.7777777777778" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="5" t="s">
-        <v>110</v>
+      <c r="A2" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>111</v>
+      <c r="A3" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>112</v>
+      <c r="A4" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>113</v>
+      <c r="A5" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>114</v>
+      <c r="A6" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>115</v>
+      <c r="A7" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
-        <v>116</v>
+      <c r="A8" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>117</v>
+      <c r="A9" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>118</v>
+      <c r="A10" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
-        <v>119</v>
+      <c r="A11" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>120</v>
+      <c r="A12" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>121</v>
+      <c r="A13" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>122</v>
+      <c r="A14" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>123</v>
+      <c r="A15" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>124</v>
+      <c r="A16" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
-        <v>125</v>
+      <c r="A17" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
-        <v>126</v>
+      <c r="A18" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>127</v>
+      <c r="A19" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
-        <v>128</v>
+      <c r="A20" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>129</v>
+      <c r="A21" s="3" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>130</v>
+      <c r="A22" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
-        <v>131</v>
+      <c r="A23" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="5" t="s">
-        <v>132</v>
+      <c r="A24" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
-        <v>133</v>
+      <c r="A25" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="5" t="s">
-        <v>134</v>
+      <c r="A26" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>135</v>
+      <c r="A27" s="3" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
-        <v>136</v>
+      <c r="A28" s="3" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>137</v>
+      <c r="A29" s="3" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="5" t="s">
-        <v>138</v>
+      <c r="A30" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
-        <v>139</v>
+      <c r="A31" s="3" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="9" t="s">
-        <v>141</v>
+      <c r="A33" s="7" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="9" t="s">
-        <v>142</v>
+      <c r="A34" s="7" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="9" t="s">
-        <v>143</v>
+      <c r="A35" s="7" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="9" t="s">
-        <v>144</v>
+      <c r="A36" s="7" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="9" t="s">
-        <v>145</v>
+      <c r="A37" s="7" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="9" t="s">
-        <v>146</v>
+      <c r="A38" s="7" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="9" t="s">
-        <v>147</v>
+      <c r="A39" s="7" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="9" t="s">
-        <v>148</v>
+      <c r="A40" s="7" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="9" t="s">
-        <v>149</v>
+      <c r="A41" s="7" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="9" t="s">
-        <v>150</v>
+      <c r="A42" s="7" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -4341,167 +4727,167 @@
   <dimension ref="A1:A32"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.4444444444444" style="5" customWidth="1"/>
+    <col min="1" max="1" width="16.4444444444444" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="6" t="s">
-        <v>152</v>
+      <c r="A2" s="5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="6" t="s">
-        <v>153</v>
+      <c r="A3" s="5" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
-        <v>154</v>
+      <c r="A4" s="5" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="6" t="s">
-        <v>155</v>
+      <c r="A5" s="5" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="6" t="s">
-        <v>156</v>
+      <c r="A6" s="5" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
-        <v>157</v>
+      <c r="A7" s="5" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="6" t="s">
-        <v>158</v>
+      <c r="A8" s="5" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="6" t="s">
-        <v>159</v>
+      <c r="A9" s="5" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
-        <v>160</v>
+      <c r="A10" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="6" t="s">
-        <v>161</v>
+      <c r="A11" s="5" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="6" t="s">
-        <v>162</v>
+      <c r="A12" s="5" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="6" t="s">
-        <v>163</v>
+      <c r="A13" s="5" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="6" t="s">
-        <v>164</v>
+      <c r="A14" s="5" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="6" t="s">
-        <v>165</v>
+      <c r="A15" s="5" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="6" t="s">
-        <v>166</v>
+      <c r="A16" s="5" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="6" t="s">
-        <v>167</v>
+      <c r="A17" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="6" t="s">
-        <v>168</v>
+      <c r="A18" s="5" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="6" t="s">
-        <v>169</v>
+      <c r="A19" s="5" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="6" t="s">
-        <v>170</v>
+      <c r="A20" s="5" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="6" t="s">
-        <v>171</v>
+      <c r="A21" s="5" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="6" t="s">
-        <v>172</v>
+      <c r="A22" s="5" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="6" t="s">
-        <v>173</v>
+      <c r="A23" s="5" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="6" t="s">
-        <v>174</v>
+      <c r="A24" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="6" t="s">
-        <v>175</v>
+      <c r="A25" s="5" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="6" t="s">
-        <v>176</v>
+      <c r="A26" s="5" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
-        <v>177</v>
+      <c r="A27" s="5" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="6" t="s">
-        <v>178</v>
+      <c r="A28" s="5" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="6" t="s">
-        <v>179</v>
+      <c r="A29" s="5" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="6" t="s">
-        <v>180</v>
+      <c r="A30" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="6" t="s">
-        <v>181</v>
+      <c r="A31" s="5" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="6" t="s">
-        <v>182</v>
+      <c r="A32" s="5" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -4516,212 +4902,212 @@
   <dimension ref="A1:A41"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.4444444444444" style="5" customWidth="1"/>
+    <col min="1" max="1" width="50.4444444444444" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="6" t="s">
-        <v>184</v>
+      <c r="A2" s="5" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="6" t="s">
-        <v>185</v>
+      <c r="A3" s="5" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
-        <v>186</v>
+      <c r="A4" s="5" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="6" t="s">
-        <v>187</v>
+      <c r="A5" s="5" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="6" t="s">
-        <v>188</v>
+      <c r="A6" s="5" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
-        <v>189</v>
+      <c r="A7" s="5" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="6" t="s">
-        <v>190</v>
+      <c r="A8" s="5" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="6" t="s">
-        <v>191</v>
+      <c r="A9" s="5" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
-        <v>192</v>
+      <c r="A10" s="5" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="6" t="s">
-        <v>193</v>
+      <c r="A11" s="5" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="6" t="s">
-        <v>194</v>
+      <c r="A12" s="5" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="6" t="s">
-        <v>195</v>
+      <c r="A13" s="5" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="6" t="s">
-        <v>196</v>
+      <c r="A14" s="5" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="6" t="s">
-        <v>197</v>
+      <c r="A15" s="5" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="6" t="s">
-        <v>198</v>
+      <c r="A16" s="5" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="7" t="s">
-        <v>199</v>
+      <c r="A17" s="4" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="9" t="s">
-        <v>200</v>
+      <c r="A18" s="7" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="9" t="s">
-        <v>201</v>
+      <c r="A19" s="7" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="9" t="s">
-        <v>202</v>
+      <c r="A20" s="7" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="9" t="s">
-        <v>203</v>
+      <c r="A21" s="7" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="9" t="s">
-        <v>204</v>
+      <c r="A22" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="9" t="s">
-        <v>205</v>
+      <c r="A23" s="7" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="9" t="s">
-        <v>206</v>
+      <c r="A24" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="9" t="s">
-        <v>207</v>
+      <c r="A25" s="7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="9" t="s">
-        <v>208</v>
+      <c r="A26" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="9" t="s">
-        <v>209</v>
+      <c r="A27" s="7" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="9" t="s">
-        <v>210</v>
+      <c r="A28" s="7" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="9" t="s">
-        <v>211</v>
+      <c r="A29" s="7" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="9" t="s">
-        <v>212</v>
+      <c r="A30" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="9" t="s">
-        <v>213</v>
+      <c r="A31" s="7" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="9" t="s">
-        <v>214</v>
+      <c r="A32" s="7" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="9" t="s">
-        <v>215</v>
+      <c r="A33" s="7" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="9" t="s">
-        <v>216</v>
+      <c r="A34" s="7" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="9" t="s">
-        <v>217</v>
+      <c r="A35" s="7" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="9" t="s">
-        <v>218</v>
+      <c r="A36" s="7" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="7" t="s">
-        <v>219</v>
+      <c r="A37" s="4" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="9" t="s">
-        <v>220</v>
+      <c r="A38" s="7" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="9" t="s">
-        <v>221</v>
+      <c r="A39" s="7" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="9" t="s">
-        <v>222</v>
+      <c r="A40" s="7" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="9" t="s">
-        <v>223</v>
+      <c r="A41" s="7" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -4736,192 +5122,192 @@
   <dimension ref="A1:A37"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="45.7777777777778" style="5" customWidth="1"/>
+    <col min="1" max="1" width="45.7777777777778" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="7" t="s">
-        <v>225</v>
+      <c r="A2" s="4" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="6" t="s">
-        <v>226</v>
+      <c r="A3" s="5" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
-        <v>227</v>
+      <c r="A4" s="5" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="6" t="s">
-        <v>228</v>
+      <c r="A5" s="5" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="6" t="s">
-        <v>229</v>
+      <c r="A6" s="5" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
-        <v>230</v>
+      <c r="A7" s="5" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="7" t="s">
-        <v>231</v>
+      <c r="A8" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="6" t="s">
-        <v>232</v>
+      <c r="A9" s="5" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
-        <v>233</v>
+      <c r="A10" s="5" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="6" t="s">
-        <v>234</v>
+      <c r="A11" s="5" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="6" t="s">
-        <v>235</v>
+      <c r="A12" s="5" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="6" t="s">
-        <v>236</v>
+      <c r="A13" s="5" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="6" t="s">
-        <v>237</v>
+      <c r="A14" s="5" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="6" t="s">
-        <v>238</v>
+      <c r="A15" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="6" t="s">
-        <v>239</v>
+      <c r="A16" s="5" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="6" t="s">
-        <v>240</v>
+      <c r="A17" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="6" t="s">
-        <v>241</v>
+      <c r="A18" s="5" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="6" t="s">
-        <v>242</v>
+      <c r="A19" s="5" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="6" t="s">
-        <v>243</v>
+      <c r="A20" s="5" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="6" t="s">
-        <v>244</v>
+      <c r="A21" s="5" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="6" t="s">
-        <v>245</v>
+      <c r="A22" s="5" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="6" t="s">
-        <v>246</v>
+      <c r="A23" s="5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="7" t="s">
-        <v>247</v>
+      <c r="A24" s="4" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="6" t="s">
-        <v>248</v>
+      <c r="A25" s="5" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="6" t="s">
-        <v>249</v>
+      <c r="A26" s="5" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
-        <v>250</v>
+      <c r="A27" s="5" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="6" t="s">
-        <v>251</v>
+      <c r="A28" s="5" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="6" t="s">
-        <v>252</v>
+      <c r="A29" s="5" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="6" t="s">
-        <v>253</v>
+      <c r="A30" s="5" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="7" t="s">
-        <v>254</v>
+      <c r="A31" s="4" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="6" t="s">
-        <v>255</v>
+      <c r="A32" s="5" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="6" t="s">
-        <v>256</v>
+      <c r="A33" s="5" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="6" t="s">
-        <v>257</v>
+      <c r="A34" s="5" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="6" t="s">
-        <v>258</v>
+      <c r="A35" s="5" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="6" t="s">
-        <v>259</v>
+      <c r="A36" s="5" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="6" t="s">
-        <v>260</v>
+      <c r="A37" s="5" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4936,222 +5322,222 @@
   <dimension ref="A1:A43"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.7777777777778" style="5" customWidth="1"/>
+    <col min="1" max="1" width="21.7777777777778" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="7" t="s">
-        <v>262</v>
+      <c r="A2" s="4" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="6" t="s">
-        <v>263</v>
+      <c r="A3" s="5" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
-        <v>264</v>
+      <c r="A4" s="5" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="6" t="s">
-        <v>265</v>
+      <c r="A5" s="5" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="6" t="s">
-        <v>266</v>
+      <c r="A6" s="5" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
-        <v>267</v>
+      <c r="A7" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="6" t="s">
-        <v>268</v>
+      <c r="A8" s="5" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="6" t="s">
-        <v>269</v>
+      <c r="A9" s="5" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
-        <v>270</v>
+      <c r="A10" s="5" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="6" t="s">
-        <v>271</v>
+      <c r="A11" s="5" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="6" t="s">
-        <v>272</v>
+      <c r="A12" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="6" t="s">
-        <v>273</v>
+      <c r="A13" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="6" t="s">
-        <v>274</v>
+      <c r="A14" s="5" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="6" t="s">
-        <v>275</v>
+      <c r="A15" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="6" t="s">
-        <v>276</v>
+      <c r="A16" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="6" t="s">
-        <v>277</v>
+      <c r="A17" s="5" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="6" t="s">
-        <v>278</v>
+      <c r="A18" s="5" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="6" t="s">
-        <v>279</v>
+      <c r="A19" s="5" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="6" t="s">
-        <v>280</v>
+      <c r="A20" s="5" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="6" t="s">
-        <v>281</v>
+      <c r="A21" s="5" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="6" t="s">
-        <v>282</v>
+      <c r="A22" s="5" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="6" t="s">
-        <v>283</v>
+      <c r="A23" s="5" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="6" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="6" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="6" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="6" t="s">
         <v>297</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="7" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="8" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="8" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="8" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="8" t="s">
-        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -5166,247 +5552,247 @@
   <dimension ref="A1:A48"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="41" style="5" customWidth="1"/>
+    <col min="1" max="1" width="41" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="7" t="s">
-        <v>225</v>
+      <c r="A2" s="4" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="6" t="s">
-        <v>300</v>
+      <c r="A3" s="5" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
-        <v>301</v>
+      <c r="A4" s="5" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="6" t="s">
-        <v>302</v>
+      <c r="A5" s="5" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="6" t="s">
-        <v>303</v>
+      <c r="A6" s="5" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="6" t="s">
-        <v>304</v>
+      <c r="A7" s="5" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="6" t="s">
-        <v>305</v>
+      <c r="A8" s="5" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="6" t="s">
-        <v>306</v>
+      <c r="A9" s="5" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
-        <v>307</v>
+      <c r="A10" s="5" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="7" t="s">
-        <v>308</v>
+      <c r="A11" s="4" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="6" t="s">
-        <v>309</v>
+      <c r="A12" s="5" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="6" t="s">
-        <v>310</v>
+      <c r="A13" s="5" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="6" t="s">
-        <v>311</v>
+      <c r="A14" s="5" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="6" t="s">
-        <v>312</v>
+      <c r="A15" s="5" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="6" t="s">
-        <v>313</v>
+      <c r="A16" s="5" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="6" t="s">
-        <v>314</v>
+      <c r="A17" s="5" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="6" t="s">
-        <v>315</v>
+      <c r="A18" s="5" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="6" t="s">
-        <v>316</v>
+      <c r="A19" s="5" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="6" t="s">
-        <v>317</v>
+      <c r="A20" s="5" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="6" t="s">
-        <v>79</v>
+      <c r="A21" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="6" t="s">
-        <v>318</v>
+      <c r="A22" s="5" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="6" t="s">
-        <v>319</v>
+      <c r="A23" s="5" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="6" t="s">
-        <v>320</v>
+      <c r="A24" s="5" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="6" t="s">
-        <v>321</v>
+      <c r="A25" s="5" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="6" t="s">
-        <v>322</v>
+      <c r="A26" s="5" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
-        <v>323</v>
+      <c r="A27" s="5" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="6" t="s">
-        <v>324</v>
+      <c r="A28" s="5" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="6" t="s">
-        <v>325</v>
+      <c r="A29" s="5" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="6" t="s">
-        <v>326</v>
+      <c r="A30" s="5" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="6" t="s">
-        <v>327</v>
+      <c r="A31" s="5" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="6" t="s">
-        <v>328</v>
+      <c r="A32" s="5" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="6" t="s">
-        <v>329</v>
+      <c r="A33" s="5" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="6" t="s">
-        <v>330</v>
+      <c r="A34" s="5" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="6" t="s">
-        <v>331</v>
+      <c r="A35" s="5" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="6" t="s">
-        <v>332</v>
+      <c r="A36" s="5" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="6" t="s">
-        <v>333</v>
+      <c r="A37" s="5" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="6" t="s">
-        <v>334</v>
+      <c r="A38" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="7" t="s">
-        <v>335</v>
+      <c r="A39" s="4" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="6" t="s">
-        <v>336</v>
+      <c r="A40" s="5" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="6" t="s">
-        <v>337</v>
+      <c r="A41" s="5" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="6" t="s">
-        <v>338</v>
+      <c r="A42" s="5" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="6" t="s">
-        <v>339</v>
+      <c r="A43" s="5" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="6" t="s">
-        <v>340</v>
+      <c r="A44" s="5" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="6" t="s">
-        <v>341</v>
+      <c r="A45" s="5" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="6" t="s">
-        <v>342</v>
+      <c r="A46" s="5" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="6" t="s">
-        <v>343</v>
+      <c r="A47" s="5" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="6" t="s">
-        <v>344</v>
+      <c r="A48" s="5" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/演唱会列表.xlsx
+++ b/演唱会列表.xlsx
@@ -4,25 +4,24 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324"/>
+    <workbookView windowWidth="22188" windowHeight="9324" tabRatio="644"/>
   </bookViews>
   <sheets>
     <sheet name="列表" sheetId="1" r:id="rId1"/>
-    <sheet name="统计" sheetId="2" r:id="rId2"/>
-    <sheet name="五月天2016" sheetId="3" r:id="rId3"/>
-    <sheet name="陈奕迅2016" sheetId="4" r:id="rId4"/>
-    <sheet name="伍佰2023" sheetId="5" r:id="rId5"/>
-    <sheet name="任贤齐2024" sheetId="6" r:id="rId6"/>
-    <sheet name="孙燕姿2025" sheetId="7" r:id="rId7"/>
-    <sheet name="周传雄2025" sheetId="8" r:id="rId8"/>
-    <sheet name="邓紫棋2025" sheetId="9" r:id="rId9"/>
-    <sheet name="李荣浩202601" sheetId="10" r:id="rId10"/>
-    <sheet name="伍佰2026" sheetId="11" r:id="rId11"/>
-    <sheet name="周杰伦2026" sheetId="12" r:id="rId12"/>
-    <sheet name="蔡依林202605" sheetId="13" r:id="rId13"/>
+    <sheet name="五月天201609" sheetId="3" r:id="rId2"/>
+    <sheet name="陈奕迅201610" sheetId="4" r:id="rId3"/>
+    <sheet name="伍佰202310" sheetId="5" r:id="rId4"/>
+    <sheet name="任贤齐202412" sheetId="6" r:id="rId5"/>
+    <sheet name="孙燕姿202505" sheetId="7" r:id="rId6"/>
+    <sheet name="周传雄202511" sheetId="8" r:id="rId7"/>
+    <sheet name="邓紫棋202511" sheetId="9" r:id="rId8"/>
+    <sheet name="李荣浩202601" sheetId="10" r:id="rId9"/>
+    <sheet name="伍佰202601" sheetId="11" r:id="rId10"/>
+    <sheet name="周杰伦202604" sheetId="12" r:id="rId11"/>
+    <sheet name="蔡依林202605" sheetId="13" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">五月天2016!$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">五月天201609!$A$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">列表!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,30 +41,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="497">
   <si>
     <t>歌手</t>
   </si>
@@ -107,9 +84,6 @@
   </si>
   <si>
     <t>主题围绕 “LIFE”（生活），陈奕迅亲自从数百首作品中挑选与生命相关的歌曲，希望观众能 用心感受及体会生命中发生的每件小事之影响力及重要性，并投放多一些情怀发掘人生不同的意义。</t>
-  </si>
-  <si>
-    <t>|</t>
   </si>
   <si>
     <t>五月天</t>
@@ -535,24 +509,6 @@
     <t>蔡依林全新主题巡回演唱会 "PLEASURE"，以"面对内心、找到真实自我"为核心命题，打造出一座横跨音乐、视觉与感官体验的巨型舞台。整场演出围绕"一个女孩的成长故事"展开：她从童年的花园出走，穿越现实与欲望的挑战，在一次次考验中重新拥抱自己，最终找到回归内在的稳定力量。</t>
   </si>
   <si>
-    <t>分类</t>
-  </si>
-  <si>
-    <t>总数</t>
-  </si>
-  <si>
-    <t>地点市总数</t>
-  </si>
-  <si>
-    <t>歌手总数</t>
-  </si>
-  <si>
-    <t>场次</t>
-  </si>
-  <si>
-    <t>年份总数</t>
-  </si>
-  <si>
     <t>五月天歌单</t>
   </si>
   <si>
@@ -1754,121 +1710,115 @@
     <t>蔡依林歌单</t>
   </si>
   <si>
-    <t>《SEVEN》</t>
-  </si>
-  <si>
-    <t>《红衣女孩》</t>
-  </si>
-  <si>
-    <t>《美杜莎》</t>
-  </si>
-  <si>
-    <t>《DIY》</t>
-  </si>
-  <si>
-    <t>《l'm Not Yours》</t>
-  </si>
-  <si>
-    <t>《恶之必要》</t>
-  </si>
-  <si>
-    <t>《特务J》</t>
-  </si>
-  <si>
-    <t>《大艺术家》</t>
-  </si>
-  <si>
-    <t>《你也有今天》</t>
-  </si>
-  <si>
-    <t>《热冬》</t>
-  </si>
-  <si>
-    <t>《BloodyMary》</t>
-  </si>
-  <si>
-    <t>《甜秘密》</t>
-  </si>
-  <si>
-    <t>《WomansWork》</t>
-  </si>
-  <si>
-    <t>《美人计》</t>
-  </si>
-  <si>
-    <t>《FishLove》</t>
-  </si>
-  <si>
-    <t>《诗人漫步》</t>
-  </si>
-  <si>
-    <t>《妥协》</t>
-  </si>
-  <si>
-    <t>《Pillow》</t>
-  </si>
-  <si>
-    <t>《天空》</t>
-  </si>
-  <si>
-    <t>《倒带》</t>
-  </si>
-  <si>
-    <t>《假装》</t>
-  </si>
-  <si>
-    <t>《柠檬草的味道》</t>
-  </si>
-  <si>
-    <t>《消极》</t>
-  </si>
-  <si>
-    <t>《insideout》</t>
-  </si>
-  <si>
-    <t>《Safari》</t>
-  </si>
-  <si>
-    <t>《都没差》</t>
-  </si>
-  <si>
-    <t>《日不落》</t>
-  </si>
-  <si>
-    <t>《马德里不思议》</t>
-  </si>
-  <si>
-    <t>《说爱你》</t>
-  </si>
-  <si>
-    <t>《脑公》</t>
-  </si>
-  <si>
-    <t>《花蝴蝶》</t>
-  </si>
-  <si>
-    <t>《看我72变》</t>
-  </si>
-  <si>
-    <t>《Pleasure》</t>
-  </si>
-  <si>
-    <t>《爱无赦》</t>
-  </si>
-  <si>
-    <t>《怪美的》</t>
-  </si>
-  <si>
-    <t>《The Divine Comedy:Purgatorio》(Intro)</t>
-  </si>
-  <si>
-    <t>《舞娘》</t>
-  </si>
-  <si>
-    <t>《Stars Align》</t>
-  </si>
-  <si>
-    <t>《Play我呸》</t>
+    <t>SEVEN</t>
+  </si>
+  <si>
+    <t>红衣女孩</t>
+  </si>
+  <si>
+    <t>美杜莎</t>
+  </si>
+  <si>
+    <t>DIY</t>
+  </si>
+  <si>
+    <t>l'm Not Yours</t>
+  </si>
+  <si>
+    <t>恶之必要</t>
+  </si>
+  <si>
+    <t>特务J</t>
+  </si>
+  <si>
+    <t>大艺术家</t>
+  </si>
+  <si>
+    <t>你也有今天</t>
+  </si>
+  <si>
+    <t>热冬</t>
+  </si>
+  <si>
+    <t>BloodyMary</t>
+  </si>
+  <si>
+    <t>甜秘密</t>
+  </si>
+  <si>
+    <t>Woman's Work</t>
+  </si>
+  <si>
+    <t>美人计</t>
+  </si>
+  <si>
+    <t>Fish Love</t>
+  </si>
+  <si>
+    <t>诗人漫步</t>
+  </si>
+  <si>
+    <t>妥协</t>
+  </si>
+  <si>
+    <t>Pillow</t>
+  </si>
+  <si>
+    <t>天空</t>
+  </si>
+  <si>
+    <t>倒带</t>
+  </si>
+  <si>
+    <t>假装</t>
+  </si>
+  <si>
+    <t>柠檬草的味道</t>
+  </si>
+  <si>
+    <t>消极掰</t>
+  </si>
+  <si>
+    <t>Inside Out</t>
+  </si>
+  <si>
+    <t>Safari</t>
+  </si>
+  <si>
+    <t>日不落</t>
+  </si>
+  <si>
+    <t>马德里不思议</t>
+  </si>
+  <si>
+    <t>说爱你</t>
+  </si>
+  <si>
+    <t>脑公</t>
+  </si>
+  <si>
+    <t>花蝴蝶</t>
+  </si>
+  <si>
+    <t>看我72变</t>
+  </si>
+  <si>
+    <t>Pleasure</t>
+  </si>
+  <si>
+    <t>爱无赦</t>
+  </si>
+  <si>
+    <t>怪美的</t>
+  </si>
+  <si>
+    <t>舞娘</t>
+  </si>
+  <si>
+    <t>Stars Align</t>
+  </si>
+  <si>
+    <t>Play我呸</t>
   </si>
 </sst>
 </file>
@@ -2514,7 +2464,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2524,9 +2474,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2538,9 +2485,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2874,424 +2818,397 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.4444444444444" style="9" customWidth="1"/>
-    <col min="2" max="2" width="41" style="9" customWidth="1"/>
-    <col min="3" max="3" width="26.7777777777778" style="9" customWidth="1"/>
-    <col min="4" max="4" width="12.6666666666667" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.1111111111111" style="3" customWidth="1"/>
-    <col min="6" max="6" width="28.8888888888889" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9" style="10" customWidth="1"/>
-    <col min="8" max="8" width="9" style="10"/>
-    <col min="9" max="9" width="33.4444444444444" style="11" customWidth="1"/>
+    <col min="1" max="1" width="11.4444444444444" style="7" customWidth="1"/>
+    <col min="2" max="2" width="41" style="7" customWidth="1"/>
+    <col min="3" max="3" width="26.7777777777778" style="7" customWidth="1"/>
+    <col min="4" max="4" width="12.6666666666667" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.1111111111111" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.8888888888889" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="8" customWidth="1"/>
+    <col min="8" max="8" width="9" style="8"/>
+    <col min="9" max="9" width="33.4444444444444" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:10">
-      <c r="A1" s="12" t="s">
+    <row r="1" ht="15.6" spans="1:9">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="86.4" spans="1:10">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="86.4" spans="1:9">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="8">
         <v>2016</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="8">
         <v>10</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J2" t="s">
+    </row>
+    <row r="3" ht="86.4" spans="1:9">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" ht="86.4" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="8">
+        <v>2016</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="10">
-        <v>2016</v>
-      </c>
-      <c r="H3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="11" t="s">
+    </row>
+    <row r="4" ht="86.4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="86.4" spans="1:10">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="8">
+        <v>2023</v>
+      </c>
+      <c r="H4" s="8">
+        <v>10</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="10">
-        <v>2023</v>
-      </c>
-      <c r="H4" s="10">
-        <v>10</v>
-      </c>
-      <c r="I4" s="11" t="s">
+    </row>
+    <row r="5" ht="86.4" spans="1:9">
+      <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="86.4" spans="1:10">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="8">
+        <v>2024</v>
+      </c>
+      <c r="H5" s="8">
+        <v>12</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="10">
-        <v>2024</v>
-      </c>
-      <c r="H5" s="10">
-        <v>12</v>
-      </c>
-      <c r="I5" s="11" t="s">
+    </row>
+    <row r="6" ht="144" spans="1:9">
+      <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="144" spans="1:10">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="8">
+        <v>2025</v>
+      </c>
+      <c r="H6" s="8">
+        <v>11</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="100.8" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="10">
+      <c r="G7" s="8">
         <v>2025</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H7" s="8">
         <v>11</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="100.8" spans="1:10">
-      <c r="A7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="I7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="3" t="s">
+    </row>
+    <row r="8" ht="115.2" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="8">
+        <v>2025</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" ht="115.2" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="8">
+        <v>2026</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="100.8" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="8">
+        <v>2026</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" ht="172.8" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="10">
-        <v>2025</v>
-      </c>
-      <c r="H7" s="10">
-        <v>11</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="115.2" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" ht="129.6" spans="1:9">
+      <c r="A12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="10">
-        <v>2025</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="115.2" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="10">
-        <v>2026</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" ht="100.8" spans="1:10">
-      <c r="A10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="10">
-        <v>2026</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" ht="172.8" spans="1:10">
-      <c r="A11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" ht="129.6" spans="1:10">
-      <c r="A12" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="I12" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3303,235 +3220,175 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.5555555555556" style="3" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>349</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="4" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>351</v>
+      <c r="A3" s="4" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>352</v>
+      <c r="A4" s="4" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>353</v>
+      <c r="A5" s="4" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>354</v>
+      <c r="A6" s="4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>355</v>
+      <c r="A7" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
-        <v>356</v>
+      <c r="A8" s="4" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>357</v>
+      <c r="A9" s="4" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>358</v>
+      <c r="A10" s="4" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="4" t="s">
-        <v>359</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>360</v>
+      <c r="A12" s="4" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>361</v>
+      <c r="A13" s="4" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>362</v>
+      <c r="A14" s="4" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>363</v>
+      <c r="A15" s="4" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>364</v>
+      <c r="A16" s="4" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
-        <v>365</v>
+      <c r="A17" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
-        <v>366</v>
+      <c r="A18" s="4" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>367</v>
+      <c r="A19" s="4" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
-        <v>368</v>
+      <c r="A20" s="4" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>369</v>
+      <c r="A21" s="4" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>370</v>
+      <c r="A22" s="4" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
-        <v>371</v>
+      <c r="A23" s="4" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="5" t="s">
-        <v>372</v>
+      <c r="A24" s="4" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
-        <v>373</v>
+      <c r="A25" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="5" t="s">
-        <v>374</v>
+      <c r="A26" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>375</v>
+      <c r="A27" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
-        <v>376</v>
+      <c r="A28" s="4" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>377</v>
+      <c r="A29" s="4" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
-        <v>379</v>
+      <c r="A31" s="4" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="5" t="s">
-        <v>380</v>
+      <c r="A32" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="5" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="4" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="5" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="5" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="5" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="6" t="s">
-        <v>393</v>
+      <c r="A33" s="4" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3543,175 +3400,310 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1111111111111" style="3" customWidth="1"/>
+    <col min="1" max="1" width="40.1111111111111" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>155</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="5" t="s">
-        <v>394</v>
+      <c r="A2" s="3" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>171</v>
+      <c r="A3" s="4" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>162</v>
+      <c r="A4" s="4" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>395</v>
+      <c r="A5" s="4" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>160</v>
+      <c r="A6" s="4" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>396</v>
+      <c r="A7" s="3" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
-        <v>397</v>
+      <c r="A8" s="4" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>398</v>
+      <c r="A9" s="4" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>176</v>
+      <c r="A10" s="4" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
-        <v>172</v>
+      <c r="A11" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>399</v>
+      <c r="A12" s="4" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>165</v>
+      <c r="A13" s="4" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>157</v>
+      <c r="A14" s="4" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>400</v>
+      <c r="A15" s="4" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>175</v>
+      <c r="A16" s="4" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
-        <v>156</v>
+      <c r="A17" s="4" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
-        <v>401</v>
+      <c r="A18" s="4" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>163</v>
+      <c r="A19" s="4" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
-        <v>174</v>
+      <c r="A20" s="4" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>402</v>
+      <c r="A21" s="4" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>403</v>
+      <c r="A22" s="4" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
-        <v>404</v>
+      <c r="A23" s="4" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="5" t="s">
-        <v>405</v>
+      <c r="A24" s="4" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
-        <v>164</v>
+      <c r="A25" s="4" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="5" t="s">
-        <v>166</v>
+      <c r="A26" s="3" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>169</v>
+      <c r="A27" s="4" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
-        <v>161</v>
+      <c r="A28" s="4" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>406</v>
+      <c r="A29" s="4" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="5" t="s">
-        <v>407</v>
+      <c r="A30" s="4" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
-        <v>168</v>
+      <c r="A31" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="5" t="s">
-        <v>170</v>
+      <c r="A32" s="4" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="5" t="s">
-        <v>158</v>
+      <c r="A33" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="4" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="4" t="s">
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -3723,322 +3715,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A60"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="40.1111111111111" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="4" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="5" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="4" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="5" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="5" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="4" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="5" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="5" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="5" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="5" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="5" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="5" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="5" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="5" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="5" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="5" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="5" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44.5555555555556" style="1" customWidth="1"/>
@@ -4046,207 +3723,192 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -4258,60 +3920,179 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:A33"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.4444444444444" style="3" customWidth="1"/>
+    <col min="1" max="1" width="32" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="8" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="3" cm="1">
-        <f t="array" ref="B2">COUNTA(_xlfn.UNIQUE(列表!E2:E11))</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="8" t="s">
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="3" cm="1">
-        <f t="array" ref="B3">COUNTA(_xlfn.UNIQUE(列表!A2:A10))</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="8" t="s">
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="3">
-        <f>COUNT(列表!G:G)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="8" t="s">
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="3" cm="1">
-        <f t="array" ref="B5">COUNTA(_xlfn.UNIQUE(列表!G2:G12))</f>
-        <v>6</v>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -4319,175 +4100,220 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="32" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="5" t="s">
-        <v>81</v>
+      <c r="A2" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>82</v>
+      <c r="A3" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>83</v>
+      <c r="A4" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>84</v>
+      <c r="A5" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>85</v>
+      <c r="A6" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>86</v>
+      <c r="A7" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
-        <v>87</v>
+      <c r="A8" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>88</v>
+      <c r="A9" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>89</v>
+      <c r="A10" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
-        <v>90</v>
+      <c r="A11" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>91</v>
+      <c r="A12" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>92</v>
+      <c r="A13" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>93</v>
+      <c r="A14" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>94</v>
+      <c r="A15" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>95</v>
+      <c r="A16" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
-        <v>96</v>
+      <c r="A17" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
-        <v>97</v>
+      <c r="A18" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>98</v>
+      <c r="A19" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
-        <v>99</v>
+      <c r="A20" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>100</v>
+      <c r="A21" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>101</v>
+      <c r="A22" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
-        <v>102</v>
+      <c r="A23" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="5" t="s">
-        <v>103</v>
+      <c r="A24" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
-        <v>104</v>
+      <c r="A25" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="5" t="s">
-        <v>105</v>
+      <c r="A26" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>106</v>
+      <c r="A27" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
-        <v>107</v>
+      <c r="A28" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>108</v>
+      <c r="A29" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="5" t="s">
-        <v>109</v>
+      <c r="A30" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
-        <v>110</v>
+      <c r="A31" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="5" t="s">
-        <v>111</v>
+      <c r="A32" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="5" t="s">
-        <v>112</v>
+      <c r="A33" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="6" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -4499,220 +4325,170 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.7777777777778" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.4444444444444" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
-        <v>114</v>
+      <c r="A2" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="3" t="s">
-        <v>115</v>
+      <c r="A3" s="4" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="3" t="s">
-        <v>116</v>
+      <c r="A4" s="4" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
-        <v>117</v>
+      <c r="A5" s="4" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="3" t="s">
-        <v>118</v>
+      <c r="A6" s="4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
-        <v>119</v>
+      <c r="A7" s="4" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="3" t="s">
-        <v>120</v>
+      <c r="A8" s="4" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
-        <v>121</v>
+      <c r="A9" s="4" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="3" t="s">
-        <v>122</v>
+      <c r="A10" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="3" t="s">
-        <v>123</v>
+      <c r="A11" s="4" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="3" t="s">
-        <v>124</v>
+      <c r="A12" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="3" t="s">
-        <v>125</v>
+      <c r="A13" s="4" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="3" t="s">
-        <v>126</v>
+      <c r="A14" s="4" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="3" t="s">
-        <v>127</v>
+      <c r="A15" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="3" t="s">
-        <v>128</v>
+      <c r="A16" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="3" t="s">
-        <v>129</v>
+      <c r="A17" s="4" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="3" t="s">
-        <v>130</v>
+      <c r="A18" s="4" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="3" t="s">
-        <v>131</v>
+      <c r="A19" s="4" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="3" t="s">
-        <v>132</v>
+      <c r="A20" s="4" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="3" t="s">
-        <v>133</v>
+      <c r="A21" s="4" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="3" t="s">
-        <v>134</v>
+      <c r="A22" s="4" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="3" t="s">
-        <v>135</v>
+      <c r="A23" s="4" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="3" t="s">
-        <v>136</v>
+      <c r="A24" s="4" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="3" t="s">
-        <v>137</v>
+      <c r="A25" s="4" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="3" t="s">
-        <v>138</v>
+      <c r="A26" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="3" t="s">
-        <v>139</v>
+      <c r="A27" s="4" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="3" t="s">
-        <v>140</v>
+      <c r="A28" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="3" t="s">
-        <v>141</v>
+      <c r="A29" s="4" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="3" t="s">
-        <v>142</v>
+      <c r="A30" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="3" t="s">
-        <v>143</v>
+      <c r="A31" s="4" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="7" t="s">
-        <v>154</v>
+      <c r="A32" s="4" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4724,170 +4500,215 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.4444444444444" style="3" customWidth="1"/>
+    <col min="1" max="1" width="50.4444444444444" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="5" t="s">
-        <v>156</v>
+      <c r="A2" s="4" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>157</v>
+      <c r="A3" s="4" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>158</v>
+      <c r="A4" s="4" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>159</v>
+      <c r="A5" s="4" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>160</v>
+      <c r="A6" s="4" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>161</v>
+      <c r="A7" s="4" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
-        <v>162</v>
+      <c r="A8" s="4" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>163</v>
+      <c r="A9" s="4" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>164</v>
+      <c r="A10" s="4" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
-        <v>165</v>
+      <c r="A11" s="4" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>166</v>
+      <c r="A12" s="4" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>167</v>
+      <c r="A13" s="4" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>168</v>
+      <c r="A14" s="4" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>169</v>
+      <c r="A15" s="4" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>170</v>
+      <c r="A16" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
-        <v>171</v>
+      <c r="A17" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
-        <v>172</v>
+      <c r="A18" s="6" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>173</v>
+      <c r="A19" s="6" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
-        <v>174</v>
+      <c r="A20" s="6" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>175</v>
+      <c r="A21" s="6" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>176</v>
+      <c r="A22" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
-        <v>177</v>
+      <c r="A23" s="6" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="5" t="s">
-        <v>178</v>
+      <c r="A24" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
-        <v>179</v>
+      <c r="A25" s="6" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="5" t="s">
-        <v>180</v>
+      <c r="A26" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>181</v>
+      <c r="A27" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
-        <v>182</v>
+      <c r="A28" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>183</v>
+      <c r="A29" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="5" t="s">
-        <v>184</v>
+      <c r="A30" s="6" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
-        <v>185</v>
+      <c r="A31" s="6" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="5" t="s">
-        <v>186</v>
+      <c r="A32" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="6" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -4899,215 +4720,195 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.4444444444444" style="3" customWidth="1"/>
+    <col min="1" max="1" width="45.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="5" t="s">
-        <v>188</v>
+      <c r="A2" s="3" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>189</v>
+      <c r="A3" s="4" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>190</v>
+      <c r="A4" s="4" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>191</v>
+      <c r="A5" s="4" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>192</v>
+      <c r="A6" s="4" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>193</v>
+      <c r="A7" s="4" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
-        <v>194</v>
+      <c r="A8" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>195</v>
+      <c r="A9" s="4" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>196</v>
+      <c r="A10" s="4" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
-        <v>197</v>
+      <c r="A11" s="4" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>198</v>
+      <c r="A12" s="4" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>199</v>
+      <c r="A13" s="4" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>200</v>
+      <c r="A14" s="4" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>201</v>
+      <c r="A15" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>202</v>
+      <c r="A16" s="4" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="4" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="7" t="s">
-        <v>204</v>
+      <c r="A18" s="4" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="7" t="s">
-        <v>205</v>
+      <c r="A19" s="4" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="7" t="s">
-        <v>206</v>
+      <c r="A20" s="4" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="7" t="s">
-        <v>207</v>
+      <c r="A21" s="4" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="7" t="s">
-        <v>208</v>
+      <c r="A22" s="4" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="7" t="s">
-        <v>209</v>
+      <c r="A23" s="4" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="7" t="s">
-        <v>210</v>
+      <c r="A24" s="3" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="7" t="s">
-        <v>211</v>
+      <c r="A25" s="4" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="7" t="s">
-        <v>212</v>
+      <c r="A26" s="4" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="7" t="s">
-        <v>213</v>
+      <c r="A27" s="4" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="7" t="s">
-        <v>214</v>
+      <c r="A28" s="4" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="7" t="s">
-        <v>215</v>
+      <c r="A29" s="4" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="7" t="s">
-        <v>216</v>
+      <c r="A30" s="4" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="7" t="s">
-        <v>217</v>
+      <c r="A31" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="7" t="s">
-        <v>218</v>
+      <c r="A32" s="4" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="7" t="s">
-        <v>219</v>
+      <c r="A33" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="7" t="s">
-        <v>220</v>
+      <c r="A34" s="4" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="7" t="s">
-        <v>221</v>
+      <c r="A35" s="4" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="7" t="s">
-        <v>222</v>
+      <c r="A36" s="4" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="7" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -5119,195 +4920,225 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="45.7777777777778" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
-        <v>229</v>
+      <c r="A2" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>230</v>
+      <c r="A3" s="4" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>231</v>
+      <c r="A4" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>232</v>
+      <c r="A5" s="4" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>233</v>
+      <c r="A6" s="4" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>234</v>
+      <c r="A7" s="4" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="4" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>236</v>
+      <c r="A9" s="4" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>237</v>
+      <c r="A10" s="4" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
-        <v>238</v>
+      <c r="A11" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>239</v>
+      <c r="A12" s="4" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>240</v>
+      <c r="A13" s="4" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>241</v>
+      <c r="A14" s="4" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>242</v>
+      <c r="A15" s="4" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>243</v>
+      <c r="A16" s="4" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
-        <v>244</v>
+      <c r="A17" s="4" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
-        <v>245</v>
+      <c r="A18" s="4" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>246</v>
+      <c r="A19" s="4" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
-        <v>247</v>
+      <c r="A20" s="4" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>248</v>
+      <c r="A21" s="4" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>249</v>
+      <c r="A22" s="4" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
-        <v>250</v>
+      <c r="A23" s="4" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="4" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
-        <v>252</v>
+      <c r="A25" s="4" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="5" t="s">
-        <v>253</v>
+      <c r="A26" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>254</v>
+      <c r="A27" s="4" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
-        <v>255</v>
+      <c r="A28" s="4" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>256</v>
+      <c r="A29" s="4" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="5" t="s">
-        <v>257</v>
+      <c r="A30" s="4" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="4" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="5" t="s">
-        <v>259</v>
+      <c r="A32" s="4" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="5" t="s">
-        <v>260</v>
+      <c r="A33" s="4" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="5" t="s">
-        <v>261</v>
+      <c r="A34" s="4" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="5" t="s">
-        <v>262</v>
+      <c r="A35" s="4" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="5" t="s">
-        <v>263</v>
+      <c r="A36" s="4" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="5" t="s">
-        <v>264</v>
+      <c r="A37" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -5319,225 +5150,250 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.7777777777778" style="3" customWidth="1"/>
+    <col min="1" max="1" width="41" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
-        <v>266</v>
+      <c r="A2" s="3" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>267</v>
+      <c r="A3" s="4" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>268</v>
+      <c r="A4" s="4" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>269</v>
+      <c r="A5" s="4" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>270</v>
+      <c r="A6" s="4" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>271</v>
+      <c r="A7" s="4" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
-        <v>272</v>
+      <c r="A8" s="4" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>273</v>
+      <c r="A9" s="4" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>274</v>
+      <c r="A10" s="4" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
-        <v>275</v>
+      <c r="A11" s="3" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>276</v>
+      <c r="A12" s="4" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>277</v>
+      <c r="A13" s="4" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>278</v>
+      <c r="A14" s="4" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>279</v>
+      <c r="A15" s="4" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>280</v>
+      <c r="A16" s="4" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
-        <v>281</v>
+      <c r="A17" s="4" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
-        <v>282</v>
+      <c r="A18" s="4" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>283</v>
+      <c r="A19" s="4" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
-        <v>284</v>
+      <c r="A20" s="4" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>285</v>
+      <c r="A21" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>286</v>
+      <c r="A22" s="4" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
-        <v>287</v>
+      <c r="A23" s="4" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="5" t="s">
-        <v>288</v>
+      <c r="A24" s="4" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
-        <v>289</v>
+      <c r="A25" s="4" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="5" t="s">
-        <v>290</v>
+      <c r="A26" s="4" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>291</v>
+      <c r="A27" s="4" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
-        <v>292</v>
+      <c r="A28" s="4" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>293</v>
+      <c r="A29" s="4" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="5" t="s">
-        <v>294</v>
+      <c r="A30" s="4" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
-        <v>295</v>
+      <c r="A31" s="4" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="5" t="s">
-        <v>296</v>
+      <c r="A32" s="4" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="5" t="s">
-        <v>297</v>
+      <c r="A33" s="4" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="5" t="s">
-        <v>298</v>
+      <c r="A34" s="4" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="5" t="s">
-        <v>299</v>
+      <c r="A35" s="4" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="5" t="s">
-        <v>300</v>
+      <c r="A36" s="4" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="5" t="s">
-        <v>301</v>
+      <c r="A37" s="4" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="4" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="6" t="s">
-        <v>293</v>
+      <c r="A39" s="3" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="6" t="s">
-        <v>294</v>
+      <c r="A40" s="4" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="6" t="s">
-        <v>295</v>
+      <c r="A41" s="4" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="6" t="s">
-        <v>284</v>
+      <c r="A42" s="4" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="6" t="s">
-        <v>297</v>
+      <c r="A43" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="4" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -5549,250 +5405,235 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="41" style="3" customWidth="1"/>
+    <col min="1" max="1" width="43.5555555555556" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
-        <v>229</v>
+      <c r="A2" s="3" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
-        <v>304</v>
+      <c r="A3" s="4" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>305</v>
+      <c r="A4" s="4" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
-        <v>306</v>
+      <c r="A5" s="4" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
-        <v>307</v>
+      <c r="A6" s="4" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>308</v>
+      <c r="A7" s="4" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
-        <v>309</v>
+      <c r="A8" s="4" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
-        <v>310</v>
+      <c r="A9" s="4" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
-        <v>311</v>
+      <c r="A10" s="4" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="4" t="s">
-        <v>312</v>
+      <c r="A11" s="3" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
-        <v>313</v>
+      <c r="A12" s="4" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
-        <v>314</v>
+      <c r="A13" s="4" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
-        <v>315</v>
+      <c r="A14" s="4" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>316</v>
+      <c r="A15" s="4" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
-        <v>317</v>
+      <c r="A16" s="4" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5" t="s">
-        <v>318</v>
+      <c r="A17" s="4" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5" t="s">
-        <v>319</v>
+      <c r="A18" s="4" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>320</v>
+      <c r="A19" s="4" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5" t="s">
-        <v>321</v>
+      <c r="A20" s="4" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>83</v>
+      <c r="A21" s="4" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>322</v>
+      <c r="A22" s="4" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
-        <v>323</v>
+      <c r="A23" s="4" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="5" t="s">
-        <v>324</v>
+      <c r="A24" s="4" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5" t="s">
-        <v>325</v>
+      <c r="A25" s="4" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="5" t="s">
-        <v>326</v>
+      <c r="A26" s="4" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>327</v>
+      <c r="A27" s="4" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="5" t="s">
-        <v>328</v>
+      <c r="A28" s="4" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>329</v>
+      <c r="A29" s="4" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="5" t="s">
-        <v>330</v>
+      <c r="A30" s="3" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
-        <v>331</v>
+      <c r="A31" s="4" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="5" t="s">
-        <v>332</v>
+      <c r="A32" s="4" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="5" t="s">
-        <v>333</v>
+      <c r="A33" s="4" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="5" t="s">
-        <v>334</v>
+      <c r="A34" s="4" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="5" t="s">
-        <v>335</v>
+      <c r="A35" s="4" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="5" t="s">
-        <v>336</v>
+      <c r="A36" s="3" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="5" t="s">
-        <v>337</v>
+      <c r="A37" s="4" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="5" t="s">
-        <v>338</v>
+      <c r="A38" s="4" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="4" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="5" t="s">
-        <v>340</v>
+      <c r="A40" s="4" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="5" t="s">
-        <v>341</v>
+      <c r="A41" s="4" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="5" t="s">
-        <v>342</v>
+      <c r="A42" s="4" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="5" t="s">
-        <v>343</v>
+      <c r="A43" s="4" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="5" t="s">
-        <v>344</v>
+      <c r="A44" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="5" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="5" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>

--- a/演唱会列表.xlsx
+++ b/演唱会列表.xlsx
@@ -19,6 +19,7 @@
     <sheet name="伍佰202601" sheetId="11" r:id="rId10"/>
     <sheet name="周杰伦202604" sheetId="12" r:id="rId11"/>
     <sheet name="蔡依林202605" sheetId="13" r:id="rId12"/>
+    <sheet name="李荣浩202605" sheetId="14" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">五月天201609!$A$1</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="515">
   <si>
     <t>歌手</t>
   </si>
@@ -1820,6 +1821,81 @@
   <si>
     <t>Play我呸</t>
   </si>
+  <si>
+    <t>歌单</t>
+  </si>
+  <si>
+    <t>黑马 + 快让我在雪地上撒点野</t>
+  </si>
+  <si>
+    <t>talking + 慢冷</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>talking</t>
+  </si>
+  <si>
+    <t>不搭</t>
+  </si>
+  <si>
+    <t>紫金花盛开</t>
+  </si>
+  <si>
+    <t>女儿国</t>
+  </si>
+  <si>
+    <t>李白 + 乐队展示</t>
+  </si>
+  <si>
+    <t>抽奖环节</t>
+  </si>
+  <si>
+    <t>作曲家 + 一百</t>
+  </si>
+  <si>
+    <t>不再见 + 拿走了什么 + 慢慢喜欢你 + 丑八怪</t>
+  </si>
+  <si>
+    <t>不遗憾 + 麻雀</t>
+  </si>
+  <si>
+    <t>花车巡游：海陆风 + 太坦白</t>
+  </si>
+  <si>
+    <t>我看着你的时候</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14.05"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">🎤 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14.05"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>点歌环节曲目</t>
+    </r>
+  </si>
+  <si>
+    <t>自拍</t>
+  </si>
+  <si>
+    <t>纵横四海</t>
+  </si>
 </sst>
 </file>
 
@@ -1831,7 +1907,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1842,6 +1918,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.05"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2334,137 +2418,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2474,6 +2558,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2495,10 +2585,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2821,43 +2911,43 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.4444444444444" style="7" customWidth="1"/>
-    <col min="2" max="2" width="41" style="7" customWidth="1"/>
-    <col min="3" max="3" width="26.7777777777778" style="7" customWidth="1"/>
-    <col min="4" max="4" width="12.6666666666667" style="7" customWidth="1"/>
+    <col min="1" max="1" width="11.4444444444444" style="9" customWidth="1"/>
+    <col min="2" max="2" width="41" style="9" customWidth="1"/>
+    <col min="3" max="3" width="26.7777777777778" style="9" customWidth="1"/>
+    <col min="4" max="4" width="12.6666666666667" style="9" customWidth="1"/>
     <col min="5" max="5" width="14.1111111111111" style="1" customWidth="1"/>
     <col min="6" max="6" width="28.8888888888889" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="8" customWidth="1"/>
-    <col min="8" max="8" width="9" style="8"/>
-    <col min="9" max="9" width="33.4444444444444" style="9" customWidth="1"/>
+    <col min="7" max="7" width="9" style="10" customWidth="1"/>
+    <col min="8" max="8" width="9" style="10"/>
+    <col min="9" max="9" width="33.4444444444444" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" spans="1:9">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2880,13 +2970,13 @@
       <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="10">
         <v>2016</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="10">
         <v>10</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="11" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2909,13 +2999,13 @@
       <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="10">
         <v>2016</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2938,13 +3028,13 @@
       <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="10">
         <v>2023</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="10">
         <v>10</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2967,13 +3057,13 @@
       <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="10">
         <v>2024</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="10">
         <v>12</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="11" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2996,13 +3086,13 @@
       <c r="F6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="10">
         <v>2025</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="10">
         <v>11</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="14" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3025,13 +3115,13 @@
       <c r="F7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="10">
         <v>2025</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="10">
         <v>11</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="15" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3054,13 +3144,13 @@
       <c r="F8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="10">
         <v>2025</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="11" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3083,13 +3173,13 @@
       <c r="F9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="10">
         <v>2026</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="15" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3112,13 +3202,13 @@
       <c r="F10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="10">
         <v>2026</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3141,21 +3231,21 @@
       <c r="F11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" ht="129.6" spans="1:9">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -3170,21 +3260,44 @@
       <c r="F12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+    <row r="13" ht="100.8" spans="1:9">
+      <c r="A13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1"/>
@@ -3232,162 +3345,162 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="6" t="s">
         <v>151</v>
       </c>
     </row>
@@ -3412,297 +3525,297 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="5" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="6" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="5" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="6" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="6" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="6" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="6" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="6" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="6" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="6" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="6" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="6" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="6" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="6" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="6" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="6" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="6" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="5" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="6" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="6" t="s">
         <v>458</v>
       </c>
     </row>
@@ -3917,6 +4030,206 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A37"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="50.6666666666667" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="35" ht="17.4" spans="1:1">
+      <c r="A35" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -3932,162 +4245,162 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="6" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4267,52 +4580,52 @@
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="8" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="8" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="8" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="8" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="8" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="8" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="8" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="8" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="8" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4337,157 +4650,157 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4512,202 +4825,202 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="8" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="8" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="8" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="8" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="8" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="8" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="8" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="8" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="8" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="8" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="8" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="8" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="8" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="8" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="8" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="8" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="8" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="8" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="8" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="8" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="8" t="s">
         <v>220</v>
       </c>
     </row>
@@ -4732,182 +5045,182 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="6" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="6" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>257</v>
       </c>
     </row>
@@ -4932,212 +5245,212 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="6" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="6" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="7" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="7" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="7" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="7" t="s">
         <v>290</v>
       </c>
     </row>
@@ -5162,237 +5475,237 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="6" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="6" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="6" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="6" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="6" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="6" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="6" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="6" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="6" t="s">
         <v>341</v>
       </c>
     </row>
@@ -5417,222 +5730,222 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="6" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="6" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="6" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="6" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="6" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="5" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="7" t="s">
         <v>386</v>
       </c>
     </row>

--- a/演唱会列表.xlsx
+++ b/演唱会列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324" tabRatio="644"/>
+    <workbookView windowWidth="22188" windowHeight="9324" tabRatio="644" firstSheet="5" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="列表" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="513">
   <si>
     <t>歌手</t>
   </si>
@@ -1825,18 +1825,15 @@
     <t>歌单</t>
   </si>
   <si>
-    <t>黑马 + 快让我在雪地上撒点野</t>
-  </si>
-  <si>
-    <t>talking + 慢冷</t>
+    <t>快让我在雪地上撒点野</t>
+  </si>
+  <si>
+    <t>talking</t>
   </si>
   <si>
     <t>VCR</t>
   </si>
   <si>
-    <t>talking</t>
-  </si>
-  <si>
     <t>不搭</t>
   </si>
   <si>
@@ -1846,19 +1843,16 @@
     <t>女儿国</t>
   </si>
   <si>
-    <t>李白 + 乐队展示</t>
-  </si>
-  <si>
-    <t>抽奖环节</t>
-  </si>
-  <si>
-    <t>作曲家 + 一百</t>
-  </si>
-  <si>
-    <t>不再见 + 拿走了什么 + 慢慢喜欢你 + 丑八怪</t>
-  </si>
-  <si>
-    <t>不遗憾 + 麻雀</t>
+    <t>不再见</t>
+  </si>
+  <si>
+    <t>拿走了什么</t>
+  </si>
+  <si>
+    <t>慢慢喜欢你</t>
+  </si>
+  <si>
+    <t>丑八怪</t>
   </si>
   <si>
     <t>花车巡游：海陆风 + 太坦白</t>
@@ -4033,7 +4027,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="50.6666666666667" style="1" customWidth="1"/>
@@ -4046,12 +4040,12 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>498</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>346</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4061,167 +4055,187 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>500</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="3" t="s">
-        <v>348</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="3" t="s">
-        <v>501</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="3" t="s">
-        <v>353</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="3" t="s">
-        <v>501</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="3" t="s">
-        <v>370</v>
+        <v>499</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="3" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="3" t="s">
-        <v>502</v>
+        <v>354</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
-        <v>360</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3" t="s">
-        <v>503</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3" t="s">
-        <v>506</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="3" t="s">
-        <v>507</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="3" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="3" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="3" t="s">
-        <v>357</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3" t="s">
-        <v>510</v>
+        <v>367</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="3" t="s">
-        <v>365</v>
+        <v>499</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="35" ht="17.4" spans="1:1">
-      <c r="A35" s="4" t="s">
-        <v>512</v>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="3" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="3" t="s">
-        <v>513</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="3" t="s">
-        <v>514</v>
+        <v>509</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="39" ht="17.4" spans="1:1">
+      <c r="A39" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="3" t="s">
+        <v>512</v>
       </c>
     </row>
   </sheetData>
